--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -1,112 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyVariant" sheetId="1" r:id="rId1"/>
+    <sheet name="EnemyVariant" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>EnemyVariant</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>map</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>04a17606a419bd3e</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>template_id</t>
-  </si>
-  <si>
-    <t>ai_graph_id</t>
-  </si>
-  <si>
-    <t>mechanically_distinct_key</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;ContentIdentity.id&gt;</t>
-  </si>
-  <si>
-    <t>ref&lt;EnemyTemplate.id&gt;</t>
-  </si>
-  <si>
-    <t>ref&lt;AiGraph.id&gt;</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>length=1..160</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -125,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -419,124 +407,468 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>24</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>EnemyVariant</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>04a17606a419bd3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>template_id</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ai_graph_id</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>mechanically_distinct_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>template_id</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ai_graph_id</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>mechanically_distinct_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;ContentIdentity.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ref&lt;EnemyTemplate.id&gt;</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ref&lt;AiGraph.id&gt;</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>length=1..160</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10006</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13006</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>101</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10007</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13007</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>enemy.eclipse-wolftrooper.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>102</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10008</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13008</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>103</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10009</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13009</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>enemy.flamespawn.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>104</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10010</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13010</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>enemy.frostspawn.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>105</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10011</v>
+      </c>
+      <c r="D13" t="n">
+        <v>13011</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>enemy.harmonious-choir-the-great-septimus.bigboss.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>106</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10012</v>
+      </c>
+      <c r="D14" t="n">
+        <v>13012</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>107</v>
+      </c>
+      <c r="C15" t="n">
+        <v>10013</v>
+      </c>
+      <c r="D15" t="n">
+        <v>13013</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>108</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10014</v>
+      </c>
+      <c r="D16" t="n">
+        <v>13014</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>109</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10015</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13015</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>enemy.sableclaw-wolftrooper.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>110</v>
+      </c>
+      <c r="C18" t="n">
+        <v>10016</v>
+      </c>
+      <c r="D18" t="n">
+        <v>13016</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>111</v>
+      </c>
+      <c r="C19" t="n">
+        <v>10017</v>
+      </c>
+      <c r="D19" t="n">
+        <v>13017</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>enemy.voidranger-trampler.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>95</v>
+      </c>
+      <c r="C20" t="n">
+        <v>10001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13001</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>96</v>
+      </c>
+      <c r="C21" t="n">
+        <v>10002</v>
+      </c>
+      <c r="D21" t="n">
+        <v>13002</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>97</v>
+      </c>
+      <c r="C22" t="n">
+        <v>10003</v>
+      </c>
+      <c r="D22" t="n">
+        <v>13003</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>enemy.automaton-spider.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>98</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10004</v>
+      </c>
+      <c r="D23" t="n">
+        <v>13004</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>99</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10005</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13005</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,6 +871,22 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C25" t="n">
+        <v>980002</v>
+      </c>
+      <c r="D25" t="n">
+        <v>980010</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,6 +887,22 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>990002</v>
+      </c>
+      <c r="D26" t="n">
+        <v>990010</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,6 +903,22 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1000002</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,6 +919,22 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1010002</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>enemy.blaze-out-of-space.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,6 +935,22 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1020002</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1020010</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -951,6 +951,22 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1030002</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1030010</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>enemy.cocolia-complete.littleboss.variant.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -967,6 +967,22 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1040002</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1040010</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>enemy.gepard-complete.littleboss.variant.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,6 +983,22 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1050002</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1050010</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>enemy.ice-out-of-space.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,6 +999,22 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1060002</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1060010</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,6 +1015,22 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1070002</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1070010</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,6 +1031,22 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1080002</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1080010</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>enemy.svarog-complete.littleboss.variant.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,257 +793,417 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C20" t="n">
-        <v>10001</v>
+        <v>10003</v>
       </c>
       <c r="D20" t="n">
-        <v>13001</v>
+        <v>13003</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
+          <t>enemy.automaton-spider.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C21" t="n">
-        <v>10002</v>
+        <v>10004</v>
       </c>
       <c r="D21" t="n">
-        <v>13002</v>
+        <v>13004</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
+          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C22" t="n">
-        <v>10003</v>
+        <v>10005</v>
       </c>
       <c r="D22" t="n">
-        <v>13003</v>
+        <v>13005</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>enemy.automaton-spider.minionlv2.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C23" t="n">
-        <v>10004</v>
+        <v>980002</v>
       </c>
       <c r="D23" t="n">
-        <v>13004</v>
+        <v>980010</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
+          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>99</v>
+        <v>990001</v>
       </c>
       <c r="C24" t="n">
-        <v>10005</v>
+        <v>990002</v>
       </c>
       <c r="D24" t="n">
-        <v>13005</v>
+        <v>990010</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
+          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C25" t="n">
-        <v>980002</v>
+        <v>1000002</v>
       </c>
       <c r="D25" t="n">
-        <v>980010</v>
+        <v>1000010</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
+          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C26" t="n">
-        <v>990002</v>
+        <v>1010002</v>
       </c>
       <c r="D26" t="n">
-        <v>990010</v>
+        <v>1010010</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
+          <t>enemy.blaze-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C27" t="n">
-        <v>1000002</v>
+        <v>1020002</v>
       </c>
       <c r="D27" t="n">
-        <v>1000010</v>
+        <v>1020010</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
+          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C28" t="n">
-        <v>1010002</v>
+        <v>1030002</v>
       </c>
       <c r="D28" t="n">
-        <v>1010010</v>
+        <v>1030010</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>enemy.blaze-out-of-space.elite.variant.01</t>
+          <t>enemy.cocolia-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C29" t="n">
-        <v>1020002</v>
+        <v>1040002</v>
       </c>
       <c r="D29" t="n">
-        <v>1020010</v>
+        <v>1040010</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
+          <t>enemy.gepard-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C30" t="n">
-        <v>1030002</v>
+        <v>1050002</v>
       </c>
       <c r="D30" t="n">
-        <v>1030010</v>
+        <v>1050010</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>enemy.cocolia-complete.littleboss.variant.01</t>
+          <t>enemy.ice-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C31" t="n">
-        <v>1040002</v>
+        <v>1060002</v>
       </c>
       <c r="D31" t="n">
-        <v>1040010</v>
+        <v>1060010</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>enemy.gepard-complete.littleboss.variant.01</t>
+          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C32" t="n">
-        <v>1050002</v>
+        <v>1070002</v>
       </c>
       <c r="D32" t="n">
-        <v>1050010</v>
+        <v>1070010</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>enemy.ice-out-of-space.elite.variant.01</t>
+          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C33" t="n">
-        <v>1060002</v>
+        <v>1080002</v>
       </c>
       <c r="D33" t="n">
-        <v>1060010</v>
+        <v>1080010</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
+          <t>enemy.svarog-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1070001</v>
+        <v>95</v>
       </c>
       <c r="C34" t="n">
-        <v>1070002</v>
+        <v>10001</v>
       </c>
       <c r="D34" t="n">
-        <v>1070010</v>
+        <v>1090041</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1080001</v>
+        <v>1090002</v>
       </c>
       <c r="C35" t="n">
-        <v>1080002</v>
+        <v>1090022</v>
       </c>
       <c r="D35" t="n">
-        <v>1080010</v>
+        <v>1090042</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>enemy.svarog-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1090023</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1090043</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1090024</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1090044</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1090025</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1090045</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>enemy.antibaryon.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1090026</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1090046</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>96</v>
+      </c>
+      <c r="C40" t="n">
+        <v>10002</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1090028</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1090048</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1090029</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1090049</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1090030</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1090050</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>enemy.automaton-direwolf.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1090031</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>enemy.automaton-grizzly.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1090032</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1090052</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>enemy.automaton-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,609 +601,753 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>10006</v>
+        <v>10007</v>
       </c>
       <c r="D8" t="n">
-        <v>13006</v>
+        <v>13007</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
+          <t>enemy.eclipse-wolftrooper.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" t="n">
-        <v>10007</v>
+        <v>10008</v>
       </c>
       <c r="D9" t="n">
-        <v>13007</v>
+        <v>13008</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>enemy.eclipse-wolftrooper.minionlv2.variant.01</t>
+          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C10" t="n">
-        <v>10008</v>
+        <v>10009</v>
       </c>
       <c r="D10" t="n">
-        <v>13008</v>
+        <v>13009</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
+          <t>enemy.flamespawn.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" t="n">
-        <v>10009</v>
+        <v>10010</v>
       </c>
       <c r="D11" t="n">
-        <v>13009</v>
+        <v>13010</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>enemy.flamespawn.minion.variant.01</t>
+          <t>enemy.frostspawn.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C12" t="n">
-        <v>10010</v>
+        <v>10011</v>
       </c>
       <c r="D12" t="n">
-        <v>13010</v>
+        <v>13011</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>enemy.frostspawn.minion.variant.01</t>
+          <t>enemy.harmonious-choir-the-great-septimus.bigboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" t="n">
-        <v>10011</v>
+        <v>10012</v>
       </c>
       <c r="D13" t="n">
-        <v>13011</v>
+        <v>13012</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>enemy.harmonious-choir-the-great-septimus.bigboss.variant.01</t>
+          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C14" t="n">
-        <v>10012</v>
+        <v>10013</v>
       </c>
       <c r="D14" t="n">
-        <v>13012</v>
+        <v>13013</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
+          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C15" t="n">
-        <v>10013</v>
+        <v>10014</v>
       </c>
       <c r="D15" t="n">
-        <v>13013</v>
+        <v>13014</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
+          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16" t="n">
-        <v>10014</v>
+        <v>10015</v>
       </c>
       <c r="D16" t="n">
-        <v>13014</v>
+        <v>13015</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
+          <t>enemy.sableclaw-wolftrooper.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C17" t="n">
-        <v>10015</v>
+        <v>10016</v>
       </c>
       <c r="D17" t="n">
-        <v>13015</v>
+        <v>13016</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>enemy.sableclaw-wolftrooper.minionlv2.variant.01</t>
+          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C18" t="n">
-        <v>10016</v>
+        <v>10017</v>
       </c>
       <c r="D18" t="n">
-        <v>13016</v>
+        <v>13017</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
+          <t>enemy.voidranger-trampler.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C19" t="n">
-        <v>10017</v>
+        <v>10004</v>
       </c>
       <c r="D19" t="n">
-        <v>13017</v>
+        <v>13004</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>enemy.voidranger-trampler.elite.variant.01</t>
+          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>97</v>
+        <v>980001</v>
       </c>
       <c r="C20" t="n">
-        <v>10003</v>
+        <v>980002</v>
       </c>
       <c r="D20" t="n">
-        <v>13003</v>
+        <v>980010</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>enemy.automaton-spider.minionlv2.variant.01</t>
+          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>98</v>
+        <v>990001</v>
       </c>
       <c r="C21" t="n">
-        <v>10004</v>
+        <v>990002</v>
       </c>
       <c r="D21" t="n">
-        <v>13004</v>
+        <v>990010</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
+          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>99</v>
+        <v>1000001</v>
       </c>
       <c r="C22" t="n">
-        <v>10005</v>
+        <v>1000002</v>
       </c>
       <c r="D22" t="n">
-        <v>13005</v>
+        <v>1000010</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
+          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C23" t="n">
-        <v>980002</v>
+        <v>1010002</v>
       </c>
       <c r="D23" t="n">
-        <v>980010</v>
+        <v>1010010</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
+          <t>enemy.blaze-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C24" t="n">
-        <v>990002</v>
+        <v>1020002</v>
       </c>
       <c r="D24" t="n">
-        <v>990010</v>
+        <v>1020010</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
+          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C25" t="n">
-        <v>1000002</v>
+        <v>1030002</v>
       </c>
       <c r="D25" t="n">
-        <v>1000010</v>
+        <v>1030010</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
+          <t>enemy.cocolia-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C26" t="n">
-        <v>1010002</v>
+        <v>1040002</v>
       </c>
       <c r="D26" t="n">
-        <v>1010010</v>
+        <v>1040010</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>enemy.blaze-out-of-space.elite.variant.01</t>
+          <t>enemy.gepard-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C27" t="n">
-        <v>1020002</v>
+        <v>1050002</v>
       </c>
       <c r="D27" t="n">
-        <v>1020010</v>
+        <v>1050010</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
+          <t>enemy.ice-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C28" t="n">
-        <v>1030002</v>
+        <v>1060002</v>
       </c>
       <c r="D28" t="n">
-        <v>1030010</v>
+        <v>1060010</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>enemy.cocolia-complete.littleboss.variant.01</t>
+          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C29" t="n">
-        <v>1040002</v>
+        <v>1070002</v>
       </c>
       <c r="D29" t="n">
-        <v>1040010</v>
+        <v>1070010</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>enemy.gepard-complete.littleboss.variant.01</t>
+          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C30" t="n">
-        <v>1050002</v>
+        <v>1080002</v>
       </c>
       <c r="D30" t="n">
-        <v>1050010</v>
+        <v>1080010</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>enemy.ice-out-of-space.elite.variant.01</t>
+          <t>enemy.svarog-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1060001</v>
+        <v>95</v>
       </c>
       <c r="C31" t="n">
-        <v>1060002</v>
+        <v>10001</v>
       </c>
       <c r="D31" t="n">
-        <v>1060010</v>
+        <v>1090041</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1070001</v>
+        <v>1090002</v>
       </c>
       <c r="C32" t="n">
-        <v>1070002</v>
+        <v>1090022</v>
       </c>
       <c r="D32" t="n">
-        <v>1070010</v>
+        <v>1090042</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1080001</v>
+        <v>1090003</v>
       </c>
       <c r="C33" t="n">
-        <v>1080002</v>
+        <v>1090023</v>
       </c>
       <c r="D33" t="n">
-        <v>1080010</v>
+        <v>1090043</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>enemy.svarog-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>95</v>
+        <v>1090004</v>
       </c>
       <c r="C34" t="n">
-        <v>10001</v>
+        <v>1090024</v>
       </c>
       <c r="D34" t="n">
-        <v>1090041</v>
+        <v>1090044</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
+          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090002</v>
+        <v>1090005</v>
       </c>
       <c r="C35" t="n">
-        <v>1090022</v>
+        <v>1090025</v>
       </c>
       <c r="D35" t="n">
-        <v>1090042</v>
+        <v>1090045</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
+          <t>enemy.antibaryon.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1090003</v>
+        <v>1090006</v>
       </c>
       <c r="C36" t="n">
-        <v>1090023</v>
+        <v>1090026</v>
       </c>
       <c r="D36" t="n">
-        <v>1090043</v>
+        <v>1090046</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
+          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1090004</v>
+        <v>96</v>
       </c>
       <c r="C37" t="n">
-        <v>1090024</v>
+        <v>10002</v>
       </c>
       <c r="D37" t="n">
-        <v>1090044</v>
+        <v>1090047</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
+          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1090005</v>
+        <v>1090008</v>
       </c>
       <c r="C38" t="n">
-        <v>1090025</v>
+        <v>1090028</v>
       </c>
       <c r="D38" t="n">
-        <v>1090045</v>
+        <v>1090048</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>enemy.antibaryon.minion.variant.01</t>
+          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1090006</v>
+        <v>1090009</v>
       </c>
       <c r="C39" t="n">
-        <v>1090026</v>
+        <v>1090029</v>
       </c>
       <c r="D39" t="n">
-        <v>1090046</v>
+        <v>1090049</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
+          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>96</v>
+        <v>1090010</v>
       </c>
       <c r="C40" t="n">
-        <v>10002</v>
+        <v>1090030</v>
       </c>
       <c r="D40" t="n">
-        <v>1090047</v>
+        <v>1090050</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
+          <t>enemy.automaton-direwolf.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1090008</v>
+        <v>1090011</v>
       </c>
       <c r="C41" t="n">
-        <v>1090028</v>
+        <v>1090031</v>
       </c>
       <c r="D41" t="n">
-        <v>1090048</v>
+        <v>1090051</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
+          <t>enemy.automaton-grizzly.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1090009</v>
+        <v>1090012</v>
       </c>
       <c r="C42" t="n">
-        <v>1090029</v>
+        <v>1090032</v>
       </c>
       <c r="D42" t="n">
-        <v>1090049</v>
+        <v>1090052</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
+          <t>enemy.automaton-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1090010</v>
+        <v>97</v>
       </c>
       <c r="C43" t="n">
-        <v>1090030</v>
+        <v>10003</v>
       </c>
       <c r="D43" t="n">
-        <v>1090050</v>
+        <v>1100041</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>enemy.automaton-direwolf.elite.variant.01</t>
+          <t>enemy.automaton-spider.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1090011</v>
+        <v>1100002</v>
       </c>
       <c r="C44" t="n">
-        <v>1090031</v>
+        <v>1100022</v>
       </c>
       <c r="D44" t="n">
-        <v>1090051</v>
+        <v>1100042</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>enemy.automaton-grizzly.elite.variant.01</t>
+          <t>enemy.baryon.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1090012</v>
+        <v>1100003</v>
       </c>
       <c r="C45" t="n">
-        <v>1090032</v>
+        <v>1100023</v>
       </c>
       <c r="D45" t="n">
-        <v>1090052</v>
+        <v>1100043</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>enemy.automaton-hound.minionlv2.variant.01</t>
+          <t>enemy.cloud-knights-patroller.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1100024</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1100044</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>enemy.decaying-shadow.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>99</v>
+      </c>
+      <c r="C47" t="n">
+        <v>10005</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1100045</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1100026</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1100046</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>enemy.disciples-of-sanctus-medicus-internal-alchemist.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1100027</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1100047</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>100</v>
+      </c>
+      <c r="C50" t="n">
+        <v>10006</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1100048</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1100029</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1100030</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1100031</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1100051</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-birdskull.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1100032</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1100052</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-bubble-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,737 +617,881 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>10008</v>
+        <v>10011</v>
       </c>
       <c r="D9" t="n">
-        <v>13008</v>
+        <v>13011</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
+          <t>enemy.harmonious-choir-the-great-septimus.bigboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10009</v>
+        <v>10012</v>
       </c>
       <c r="D10" t="n">
-        <v>13009</v>
+        <v>13012</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>enemy.flamespawn.minion.variant.01</t>
+          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C11" t="n">
-        <v>10010</v>
+        <v>10013</v>
       </c>
       <c r="D11" t="n">
-        <v>13010</v>
+        <v>13013</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>enemy.frostspawn.minion.variant.01</t>
+          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C12" t="n">
-        <v>10011</v>
+        <v>10014</v>
       </c>
       <c r="D12" t="n">
-        <v>13011</v>
+        <v>13014</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>enemy.harmonious-choir-the-great-septimus.bigboss.variant.01</t>
+          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C13" t="n">
-        <v>10012</v>
+        <v>10015</v>
       </c>
       <c r="D13" t="n">
-        <v>13012</v>
+        <v>13015</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
+          <t>enemy.sableclaw-wolftrooper.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C14" t="n">
-        <v>10013</v>
+        <v>10016</v>
       </c>
       <c r="D14" t="n">
-        <v>13013</v>
+        <v>13016</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
+          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C15" t="n">
-        <v>10014</v>
+        <v>10017</v>
       </c>
       <c r="D15" t="n">
-        <v>13014</v>
+        <v>13017</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
+          <t>enemy.voidranger-trampler.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C16" t="n">
-        <v>10015</v>
+        <v>10004</v>
       </c>
       <c r="D16" t="n">
-        <v>13015</v>
+        <v>13004</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>enemy.sableclaw-wolftrooper.minionlv2.variant.01</t>
+          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C17" t="n">
-        <v>10016</v>
+        <v>980002</v>
       </c>
       <c r="D17" t="n">
-        <v>13016</v>
+        <v>980010</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
+          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C18" t="n">
-        <v>10017</v>
+        <v>990002</v>
       </c>
       <c r="D18" t="n">
-        <v>13017</v>
+        <v>990010</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>enemy.voidranger-trampler.elite.variant.01</t>
+          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C19" t="n">
-        <v>10004</v>
+        <v>1000002</v>
       </c>
       <c r="D19" t="n">
-        <v>13004</v>
+        <v>1000010</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
+          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C20" t="n">
-        <v>980002</v>
+        <v>1010002</v>
       </c>
       <c r="D20" t="n">
-        <v>980010</v>
+        <v>1010010</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
+          <t>enemy.blaze-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C21" t="n">
-        <v>990002</v>
+        <v>1020002</v>
       </c>
       <c r="D21" t="n">
-        <v>990010</v>
+        <v>1020010</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
+          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C22" t="n">
-        <v>1000002</v>
+        <v>1030002</v>
       </c>
       <c r="D22" t="n">
-        <v>1000010</v>
+        <v>1030010</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
+          <t>enemy.cocolia-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C23" t="n">
-        <v>1010002</v>
+        <v>1040002</v>
       </c>
       <c r="D23" t="n">
-        <v>1010010</v>
+        <v>1040010</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>enemy.blaze-out-of-space.elite.variant.01</t>
+          <t>enemy.gepard-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C24" t="n">
-        <v>1020002</v>
+        <v>1050002</v>
       </c>
       <c r="D24" t="n">
-        <v>1020010</v>
+        <v>1050010</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
+          <t>enemy.ice-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C25" t="n">
-        <v>1030002</v>
+        <v>1060002</v>
       </c>
       <c r="D25" t="n">
-        <v>1030010</v>
+        <v>1060010</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>enemy.cocolia-complete.littleboss.variant.01</t>
+          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C26" t="n">
-        <v>1040002</v>
+        <v>1070002</v>
       </c>
       <c r="D26" t="n">
-        <v>1040010</v>
+        <v>1070010</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>enemy.gepard-complete.littleboss.variant.01</t>
+          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C27" t="n">
-        <v>1050002</v>
+        <v>1080002</v>
       </c>
       <c r="D27" t="n">
-        <v>1050010</v>
+        <v>1080010</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>enemy.ice-out-of-space.elite.variant.01</t>
+          <t>enemy.svarog-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1060001</v>
+        <v>95</v>
       </c>
       <c r="C28" t="n">
-        <v>1060002</v>
+        <v>10001</v>
       </c>
       <c r="D28" t="n">
-        <v>1060010</v>
+        <v>1090041</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1070001</v>
+        <v>1090002</v>
       </c>
       <c r="C29" t="n">
-        <v>1070002</v>
+        <v>1090022</v>
       </c>
       <c r="D29" t="n">
-        <v>1070010</v>
+        <v>1090042</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1080001</v>
+        <v>1090003</v>
       </c>
       <c r="C30" t="n">
-        <v>1080002</v>
+        <v>1090023</v>
       </c>
       <c r="D30" t="n">
-        <v>1080010</v>
+        <v>1090043</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>enemy.svarog-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>95</v>
+        <v>1090004</v>
       </c>
       <c r="C31" t="n">
-        <v>10001</v>
+        <v>1090024</v>
       </c>
       <c r="D31" t="n">
-        <v>1090041</v>
+        <v>1090044</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
+          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1090002</v>
+        <v>1090005</v>
       </c>
       <c r="C32" t="n">
-        <v>1090022</v>
+        <v>1090025</v>
       </c>
       <c r="D32" t="n">
-        <v>1090042</v>
+        <v>1090045</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
+          <t>enemy.antibaryon.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1090003</v>
+        <v>1090006</v>
       </c>
       <c r="C33" t="n">
-        <v>1090023</v>
+        <v>1090026</v>
       </c>
       <c r="D33" t="n">
-        <v>1090043</v>
+        <v>1090046</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
+          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1090004</v>
+        <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>1090024</v>
+        <v>10002</v>
       </c>
       <c r="D34" t="n">
-        <v>1090044</v>
+        <v>1090047</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
+          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090005</v>
+        <v>1090008</v>
       </c>
       <c r="C35" t="n">
-        <v>1090025</v>
+        <v>1090028</v>
       </c>
       <c r="D35" t="n">
-        <v>1090045</v>
+        <v>1090048</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>enemy.antibaryon.minion.variant.01</t>
+          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1090006</v>
+        <v>1090009</v>
       </c>
       <c r="C36" t="n">
-        <v>1090026</v>
+        <v>1090029</v>
       </c>
       <c r="D36" t="n">
-        <v>1090046</v>
+        <v>1090049</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
+          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>96</v>
+        <v>1090010</v>
       </c>
       <c r="C37" t="n">
-        <v>10002</v>
+        <v>1090030</v>
       </c>
       <c r="D37" t="n">
-        <v>1090047</v>
+        <v>1090050</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
+          <t>enemy.automaton-direwolf.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1090008</v>
+        <v>1090011</v>
       </c>
       <c r="C38" t="n">
-        <v>1090028</v>
+        <v>1090031</v>
       </c>
       <c r="D38" t="n">
-        <v>1090048</v>
+        <v>1090051</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
+          <t>enemy.automaton-grizzly.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1090009</v>
+        <v>1090012</v>
       </c>
       <c r="C39" t="n">
-        <v>1090029</v>
+        <v>1090032</v>
       </c>
       <c r="D39" t="n">
-        <v>1090049</v>
+        <v>1090052</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
+          <t>enemy.automaton-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1090010</v>
+        <v>97</v>
       </c>
       <c r="C40" t="n">
-        <v>1090030</v>
+        <v>10003</v>
       </c>
       <c r="D40" t="n">
-        <v>1090050</v>
+        <v>1100041</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>enemy.automaton-direwolf.elite.variant.01</t>
+          <t>enemy.automaton-spider.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1090011</v>
+        <v>1100002</v>
       </c>
       <c r="C41" t="n">
-        <v>1090031</v>
+        <v>1100022</v>
       </c>
       <c r="D41" t="n">
-        <v>1090051</v>
+        <v>1100042</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>enemy.automaton-grizzly.elite.variant.01</t>
+          <t>enemy.baryon.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1090012</v>
+        <v>1100003</v>
       </c>
       <c r="C42" t="n">
-        <v>1090032</v>
+        <v>1100023</v>
       </c>
       <c r="D42" t="n">
-        <v>1090052</v>
+        <v>1100043</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>enemy.automaton-hound.minionlv2.variant.01</t>
+          <t>enemy.cloud-knights-patroller.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>97</v>
+        <v>1100004</v>
       </c>
       <c r="C43" t="n">
-        <v>10003</v>
+        <v>1100024</v>
       </c>
       <c r="D43" t="n">
-        <v>1100041</v>
+        <v>1100044</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>enemy.automaton-spider.minionlv2.variant.01</t>
+          <t>enemy.decaying-shadow.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1100002</v>
+        <v>99</v>
       </c>
       <c r="C44" t="n">
-        <v>1100022</v>
+        <v>10005</v>
       </c>
       <c r="D44" t="n">
-        <v>1100042</v>
+        <v>1100045</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>enemy.baryon.minion.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1100003</v>
+        <v>1100006</v>
       </c>
       <c r="C45" t="n">
-        <v>1100023</v>
+        <v>1100026</v>
       </c>
       <c r="D45" t="n">
-        <v>1100043</v>
+        <v>1100046</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>enemy.cloud-knights-patroller.minionlv2.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-internal-alchemist.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1100004</v>
+        <v>1100007</v>
       </c>
       <c r="C46" t="n">
-        <v>1100024</v>
+        <v>1100027</v>
       </c>
       <c r="D46" t="n">
-        <v>1100044</v>
+        <v>1100047</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>enemy.decaying-shadow.elite.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C47" t="n">
-        <v>10005</v>
+        <v>10006</v>
       </c>
       <c r="D47" t="n">
-        <v>1100045</v>
+        <v>1100048</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1100006</v>
+        <v>1100009</v>
       </c>
       <c r="C48" t="n">
-        <v>1100026</v>
+        <v>1100029</v>
       </c>
       <c r="D48" t="n">
-        <v>1100046</v>
+        <v>1100049</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-internal-alchemist.minionlv2.variant.01</t>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1100007</v>
+        <v>1100010</v>
       </c>
       <c r="C49" t="n">
-        <v>1100027</v>
+        <v>1100030</v>
       </c>
       <c r="D49" t="n">
-        <v>1100047</v>
+        <v>1100050</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-shape-shifter-bug.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>100</v>
+        <v>1100011</v>
       </c>
       <c r="C50" t="n">
-        <v>10006</v>
+        <v>1100031</v>
       </c>
       <c r="D50" t="n">
-        <v>1100048</v>
+        <v>1100051</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-birdskull.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1100009</v>
+        <v>1100012</v>
       </c>
       <c r="C51" t="n">
-        <v>1100029</v>
+        <v>1100032</v>
       </c>
       <c r="D51" t="n">
-        <v>1100049</v>
+        <v>1100052</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-beyond-overcooked-bug.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-bubble-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1100010</v>
+        <v>1110001</v>
       </c>
       <c r="C52" t="n">
-        <v>1100030</v>
+        <v>1110021</v>
       </c>
       <c r="D52" t="n">
-        <v>1100050</v>
+        <v>1110041</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-beyond-overcooked.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-mr-domescreen.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1100011</v>
+        <v>1110002</v>
       </c>
       <c r="C53" t="n">
-        <v>1100031</v>
+        <v>1110022</v>
       </c>
       <c r="D53" t="n">
-        <v>1100051</v>
+        <v>1110042</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-birdskull.minion.variant.01</t>
+          <t>enemy.dreamjolt-troupes-spring-loader.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1100012</v>
+        <v>1110003</v>
       </c>
       <c r="C54" t="n">
-        <v>1100032</v>
+        <v>1110023</v>
       </c>
       <c r="D54" t="n">
-        <v>1100052</v>
+        <v>1110043</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-bubble-hound.minionlv2.variant.01</t>
+          <t>enemy.dreamjolt-troupes-sweet-gorilla-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1110024</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1110044</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-sweet-gorilla.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1110025</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1110045</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-winder-goon.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1110026</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1110046</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>enemy.entranced-ingenium-golden-cloud-toad.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>102</v>
+      </c>
+      <c r="C58" t="n">
+        <v>10008</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1110047</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1110028</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1110048</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>enemy.entranced-ingenium-obedient-dracolion.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1110029</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1110049</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>enemy.everwinter-shadewalker.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>103</v>
+      </c>
+      <c r="C61" t="n">
+        <v>10009</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1110050</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>enemy.flamespawn.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1110031</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>enemy.frigid-prowler.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>104</v>
+      </c>
+      <c r="C63" t="n">
+        <v>10010</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1110052</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>enemy.frostspawn.minion.variant.01</t>
         </is>
       </c>
     </row>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,865 +633,1009 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C10" t="n">
-        <v>10012</v>
+        <v>10015</v>
       </c>
       <c r="D10" t="n">
-        <v>13012</v>
+        <v>13015</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
+          <t>enemy.sableclaw-wolftrooper.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C11" t="n">
-        <v>10013</v>
+        <v>10016</v>
       </c>
       <c r="D11" t="n">
-        <v>13013</v>
+        <v>13016</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
+          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C12" t="n">
-        <v>10014</v>
+        <v>10017</v>
       </c>
       <c r="D12" t="n">
-        <v>13014</v>
+        <v>13017</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
+          <t>enemy.voidranger-trampler.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C13" t="n">
-        <v>10015</v>
+        <v>10004</v>
       </c>
       <c r="D13" t="n">
-        <v>13015</v>
+        <v>13004</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>enemy.sableclaw-wolftrooper.minionlv2.variant.01</t>
+          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C14" t="n">
-        <v>10016</v>
+        <v>980002</v>
       </c>
       <c r="D14" t="n">
-        <v>13016</v>
+        <v>980010</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
+          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C15" t="n">
-        <v>10017</v>
+        <v>990002</v>
       </c>
       <c r="D15" t="n">
-        <v>13017</v>
+        <v>990010</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>enemy.voidranger-trampler.elite.variant.01</t>
+          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C16" t="n">
-        <v>10004</v>
+        <v>1000002</v>
       </c>
       <c r="D16" t="n">
-        <v>13004</v>
+        <v>1000010</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
+          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C17" t="n">
-        <v>980002</v>
+        <v>1010002</v>
       </c>
       <c r="D17" t="n">
-        <v>980010</v>
+        <v>1010010</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
+          <t>enemy.blaze-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C18" t="n">
-        <v>990002</v>
+        <v>1020002</v>
       </c>
       <c r="D18" t="n">
-        <v>990010</v>
+        <v>1020010</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
+          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C19" t="n">
-        <v>1000002</v>
+        <v>1030002</v>
       </c>
       <c r="D19" t="n">
-        <v>1000010</v>
+        <v>1030010</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
+          <t>enemy.cocolia-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C20" t="n">
-        <v>1010002</v>
+        <v>1040002</v>
       </c>
       <c r="D20" t="n">
-        <v>1010010</v>
+        <v>1040010</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>enemy.blaze-out-of-space.elite.variant.01</t>
+          <t>enemy.gepard-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C21" t="n">
-        <v>1020002</v>
+        <v>1050002</v>
       </c>
       <c r="D21" t="n">
-        <v>1020010</v>
+        <v>1050010</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
+          <t>enemy.ice-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C22" t="n">
-        <v>1030002</v>
+        <v>1060002</v>
       </c>
       <c r="D22" t="n">
-        <v>1030010</v>
+        <v>1060010</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>enemy.cocolia-complete.littleboss.variant.01</t>
+          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C23" t="n">
-        <v>1040002</v>
+        <v>1070002</v>
       </c>
       <c r="D23" t="n">
-        <v>1040010</v>
+        <v>1070010</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>enemy.gepard-complete.littleboss.variant.01</t>
+          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C24" t="n">
-        <v>1050002</v>
+        <v>1080002</v>
       </c>
       <c r="D24" t="n">
-        <v>1050010</v>
+        <v>1080010</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>enemy.ice-out-of-space.elite.variant.01</t>
+          <t>enemy.svarog-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1060001</v>
+        <v>95</v>
       </c>
       <c r="C25" t="n">
-        <v>1060002</v>
+        <v>10001</v>
       </c>
       <c r="D25" t="n">
-        <v>1060010</v>
+        <v>1090041</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1070001</v>
+        <v>1090002</v>
       </c>
       <c r="C26" t="n">
-        <v>1070002</v>
+        <v>1090022</v>
       </c>
       <c r="D26" t="n">
-        <v>1070010</v>
+        <v>1090042</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1080001</v>
+        <v>1090003</v>
       </c>
       <c r="C27" t="n">
-        <v>1080002</v>
+        <v>1090023</v>
       </c>
       <c r="D27" t="n">
-        <v>1080010</v>
+        <v>1090043</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>enemy.svarog-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>95</v>
+        <v>1090004</v>
       </c>
       <c r="C28" t="n">
-        <v>10001</v>
+        <v>1090024</v>
       </c>
       <c r="D28" t="n">
-        <v>1090041</v>
+        <v>1090044</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
+          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1090002</v>
+        <v>1090005</v>
       </c>
       <c r="C29" t="n">
-        <v>1090022</v>
+        <v>1090025</v>
       </c>
       <c r="D29" t="n">
-        <v>1090042</v>
+        <v>1090045</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
+          <t>enemy.antibaryon.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1090003</v>
+        <v>1090006</v>
       </c>
       <c r="C30" t="n">
-        <v>1090023</v>
+        <v>1090026</v>
       </c>
       <c r="D30" t="n">
-        <v>1090043</v>
+        <v>1090046</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
+          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1090004</v>
+        <v>96</v>
       </c>
       <c r="C31" t="n">
-        <v>1090024</v>
+        <v>10002</v>
       </c>
       <c r="D31" t="n">
-        <v>1090044</v>
+        <v>1090047</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
+          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1090005</v>
+        <v>1090008</v>
       </c>
       <c r="C32" t="n">
-        <v>1090025</v>
+        <v>1090028</v>
       </c>
       <c r="D32" t="n">
-        <v>1090045</v>
+        <v>1090048</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>enemy.antibaryon.minion.variant.01</t>
+          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1090006</v>
+        <v>1090009</v>
       </c>
       <c r="C33" t="n">
-        <v>1090026</v>
+        <v>1090029</v>
       </c>
       <c r="D33" t="n">
-        <v>1090046</v>
+        <v>1090049</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
+          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>96</v>
+        <v>1090010</v>
       </c>
       <c r="C34" t="n">
-        <v>10002</v>
+        <v>1090030</v>
       </c>
       <c r="D34" t="n">
-        <v>1090047</v>
+        <v>1090050</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
+          <t>enemy.automaton-direwolf.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090008</v>
+        <v>1090011</v>
       </c>
       <c r="C35" t="n">
-        <v>1090028</v>
+        <v>1090031</v>
       </c>
       <c r="D35" t="n">
-        <v>1090048</v>
+        <v>1090051</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
+          <t>enemy.automaton-grizzly.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1090009</v>
+        <v>1090012</v>
       </c>
       <c r="C36" t="n">
-        <v>1090029</v>
+        <v>1090032</v>
       </c>
       <c r="D36" t="n">
-        <v>1090049</v>
+        <v>1090052</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
+          <t>enemy.automaton-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1090010</v>
+        <v>97</v>
       </c>
       <c r="C37" t="n">
-        <v>1090030</v>
+        <v>10003</v>
       </c>
       <c r="D37" t="n">
-        <v>1090050</v>
+        <v>1100041</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>enemy.automaton-direwolf.elite.variant.01</t>
+          <t>enemy.automaton-spider.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1090011</v>
+        <v>1100002</v>
       </c>
       <c r="C38" t="n">
-        <v>1090031</v>
+        <v>1100022</v>
       </c>
       <c r="D38" t="n">
-        <v>1090051</v>
+        <v>1100042</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>enemy.automaton-grizzly.elite.variant.01</t>
+          <t>enemy.baryon.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1090012</v>
+        <v>1100003</v>
       </c>
       <c r="C39" t="n">
-        <v>1090032</v>
+        <v>1100023</v>
       </c>
       <c r="D39" t="n">
-        <v>1090052</v>
+        <v>1100043</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>enemy.automaton-hound.minionlv2.variant.01</t>
+          <t>enemy.cloud-knights-patroller.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>97</v>
+        <v>1100004</v>
       </c>
       <c r="C40" t="n">
-        <v>10003</v>
+        <v>1100024</v>
       </c>
       <c r="D40" t="n">
-        <v>1100041</v>
+        <v>1100044</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>enemy.automaton-spider.minionlv2.variant.01</t>
+          <t>enemy.decaying-shadow.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1100002</v>
+        <v>99</v>
       </c>
       <c r="C41" t="n">
-        <v>1100022</v>
+        <v>10005</v>
       </c>
       <c r="D41" t="n">
-        <v>1100042</v>
+        <v>1100045</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>enemy.baryon.minion.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1100003</v>
+        <v>1100006</v>
       </c>
       <c r="C42" t="n">
-        <v>1100023</v>
+        <v>1100026</v>
       </c>
       <c r="D42" t="n">
-        <v>1100043</v>
+        <v>1100046</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>enemy.cloud-knights-patroller.minionlv2.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-internal-alchemist.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1100004</v>
+        <v>1100007</v>
       </c>
       <c r="C43" t="n">
-        <v>1100024</v>
+        <v>1100027</v>
       </c>
       <c r="D43" t="n">
-        <v>1100044</v>
+        <v>1100047</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>enemy.decaying-shadow.elite.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" t="n">
-        <v>10005</v>
+        <v>10006</v>
       </c>
       <c r="D44" t="n">
-        <v>1100045</v>
+        <v>1100048</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1100006</v>
+        <v>1100009</v>
       </c>
       <c r="C45" t="n">
-        <v>1100026</v>
+        <v>1100029</v>
       </c>
       <c r="D45" t="n">
-        <v>1100046</v>
+        <v>1100049</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-internal-alchemist.minionlv2.variant.01</t>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1100007</v>
+        <v>1100010</v>
       </c>
       <c r="C46" t="n">
-        <v>1100027</v>
+        <v>1100030</v>
       </c>
       <c r="D46" t="n">
-        <v>1100047</v>
+        <v>1100050</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-shape-shifter-bug.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>100</v>
+        <v>1100011</v>
       </c>
       <c r="C47" t="n">
-        <v>10006</v>
+        <v>1100031</v>
       </c>
       <c r="D47" t="n">
-        <v>1100048</v>
+        <v>1100051</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-birdskull.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1100009</v>
+        <v>1100012</v>
       </c>
       <c r="C48" t="n">
-        <v>1100029</v>
+        <v>1100032</v>
       </c>
       <c r="D48" t="n">
-        <v>1100049</v>
+        <v>1100052</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-beyond-overcooked-bug.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-bubble-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1100010</v>
+        <v>1110001</v>
       </c>
       <c r="C49" t="n">
-        <v>1100030</v>
+        <v>1110021</v>
       </c>
       <c r="D49" t="n">
-        <v>1100050</v>
+        <v>1110041</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-beyond-overcooked.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-mr-domescreen.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1100011</v>
+        <v>1110002</v>
       </c>
       <c r="C50" t="n">
-        <v>1100031</v>
+        <v>1110022</v>
       </c>
       <c r="D50" t="n">
-        <v>1100051</v>
+        <v>1110042</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-birdskull.minion.variant.01</t>
+          <t>enemy.dreamjolt-troupes-spring-loader.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1100012</v>
+        <v>1110003</v>
       </c>
       <c r="C51" t="n">
-        <v>1100032</v>
+        <v>1110023</v>
       </c>
       <c r="D51" t="n">
-        <v>1100052</v>
+        <v>1110043</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-bubble-hound.minionlv2.variant.01</t>
+          <t>enemy.dreamjolt-troupes-sweet-gorilla-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1110001</v>
+        <v>1110004</v>
       </c>
       <c r="C52" t="n">
-        <v>1110021</v>
+        <v>1110024</v>
       </c>
       <c r="D52" t="n">
-        <v>1110041</v>
+        <v>1110044</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-mr-domescreen.minionlv2.variant.01</t>
+          <t>enemy.dreamjolt-troupes-sweet-gorilla.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1110002</v>
+        <v>1110005</v>
       </c>
       <c r="C53" t="n">
-        <v>1110022</v>
+        <v>1110025</v>
       </c>
       <c r="D53" t="n">
-        <v>1110042</v>
+        <v>1110045</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-spring-loader.minion.variant.01</t>
+          <t>enemy.dreamjolt-troupes-winder-goon.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1110003</v>
+        <v>1110006</v>
       </c>
       <c r="C54" t="n">
-        <v>1110023</v>
+        <v>1110026</v>
       </c>
       <c r="D54" t="n">
-        <v>1110043</v>
+        <v>1110046</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-sweet-gorilla-bug.elite.variant.01</t>
+          <t>enemy.entranced-ingenium-golden-cloud-toad.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1110004</v>
+        <v>102</v>
       </c>
       <c r="C55" t="n">
-        <v>1110024</v>
+        <v>10008</v>
       </c>
       <c r="D55" t="n">
-        <v>1110044</v>
+        <v>1110047</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-sweet-gorilla.elite.variant.01</t>
+          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1110005</v>
+        <v>1110008</v>
       </c>
       <c r="C56" t="n">
-        <v>1110025</v>
+        <v>1110028</v>
       </c>
       <c r="D56" t="n">
-        <v>1110045</v>
+        <v>1110048</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-winder-goon.minionlv2.variant.01</t>
+          <t>enemy.entranced-ingenium-obedient-dracolion.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1110006</v>
+        <v>1110009</v>
       </c>
       <c r="C57" t="n">
-        <v>1110026</v>
+        <v>1110029</v>
       </c>
       <c r="D57" t="n">
-        <v>1110046</v>
+        <v>1110049</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-golden-cloud-toad.minion.variant.01</t>
+          <t>enemy.everwinter-shadewalker.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C58" t="n">
-        <v>10008</v>
+        <v>10009</v>
       </c>
       <c r="D58" t="n">
-        <v>1110047</v>
+        <v>1110050</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
+          <t>enemy.flamespawn.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1110008</v>
+        <v>1110011</v>
       </c>
       <c r="C59" t="n">
-        <v>1110028</v>
+        <v>1110031</v>
       </c>
       <c r="D59" t="n">
-        <v>1110048</v>
+        <v>1110051</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-obedient-dracolion.minion.variant.01</t>
+          <t>enemy.frigid-prowler.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1110009</v>
+        <v>104</v>
       </c>
       <c r="C60" t="n">
-        <v>1110029</v>
+        <v>10010</v>
       </c>
       <c r="D60" t="n">
-        <v>1110049</v>
+        <v>1110052</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>enemy.everwinter-shadewalker.minionlv2.variant.01</t>
+          <t>enemy.frostspawn.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>103</v>
+        <v>1120001</v>
       </c>
       <c r="C61" t="n">
-        <v>10009</v>
+        <v>1120021</v>
       </c>
       <c r="D61" t="n">
-        <v>1110050</v>
+        <v>1120041</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>enemy.flamespawn.minion.variant.01</t>
+          <t>enemy.grunt-field-personnel.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1110011</v>
+        <v>1120002</v>
       </c>
       <c r="C62" t="n">
-        <v>1110031</v>
+        <v>1120022</v>
       </c>
       <c r="D62" t="n">
-        <v>1110051</v>
+        <v>1120042</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>enemy.frigid-prowler.elite.variant.01</t>
+          <t>enemy.grunt-security-personnel.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>104</v>
+        <v>1120003</v>
       </c>
       <c r="C63" t="n">
-        <v>10010</v>
+        <v>1120023</v>
       </c>
       <c r="D63" t="n">
-        <v>1110052</v>
+        <v>1120043</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>enemy.frostspawn.minion.variant.01</t>
+          <t>enemy.guardian-shadow.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1120024</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1120044</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>enemy.imaginary-weaver.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>106</v>
+      </c>
+      <c r="C65" t="n">
+        <v>10012</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1120045</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1120026</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1120046</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>enemy.juvenile-sting.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1120027</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1120047</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>enemy.lesser-sting.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>107</v>
+      </c>
+      <c r="C68" t="n">
+        <v>10013</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1120048</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>108</v>
+      </c>
+      <c r="C69" t="n">
+        <v>10014</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1120049</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1120030</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1120050</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>enemy.mask-of-no-thought.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1120031</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1120051</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>enemy.memory-zone-meme-allseer.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1120032</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1120052</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>enemy.memory-zone-meme-heartbreaker.minionlv2.variant.01</t>
         </is>
       </c>
     </row>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1639,6 +1639,198 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1130021</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1130041</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>enemy.memory-zone-meme-shell-of-faded-rage.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1130022</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1130042</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>enemy.memory-zone-meme-something-in-the-mirror.minionlv2.variant.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1130023</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1130043</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>enemy.searing-prowler.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1130024</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1130044</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>enemy.senior-staff-team-leader-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1130025</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1130045</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>enemy.senior-staff-team-leader.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1130026</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1130046</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>enemy.silvermane-cannoneer.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1130027</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1130047</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>enemy.silvermane-gunner.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1130028</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1130048</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>enemy.silvermane-lieutenant-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1130029</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1130049</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>enemy.silvermane-soldier.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1130030</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1130050</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>enemy.stormbringer-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1130031</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1130051</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>enemy.stormbringer.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1130032</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1130052</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>enemy.the-ascended.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,1185 +649,1361 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" t="n">
-        <v>10016</v>
+        <v>10017</v>
       </c>
       <c r="D11" t="n">
-        <v>13016</v>
+        <v>13017</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
+          <t>enemy.voidranger-trampler.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C12" t="n">
-        <v>10017</v>
+        <v>10004</v>
       </c>
       <c r="D12" t="n">
-        <v>13017</v>
+        <v>13004</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>enemy.voidranger-trampler.elite.variant.01</t>
+          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C13" t="n">
-        <v>10004</v>
+        <v>980002</v>
       </c>
       <c r="D13" t="n">
-        <v>13004</v>
+        <v>980010</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
+          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C14" t="n">
-        <v>980002</v>
+        <v>990002</v>
       </c>
       <c r="D14" t="n">
-        <v>980010</v>
+        <v>990010</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
+          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C15" t="n">
-        <v>990002</v>
+        <v>1000002</v>
       </c>
       <c r="D15" t="n">
-        <v>990010</v>
+        <v>1000010</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
+          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C16" t="n">
-        <v>1000002</v>
+        <v>1010002</v>
       </c>
       <c r="D16" t="n">
-        <v>1000010</v>
+        <v>1010010</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
+          <t>enemy.blaze-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C17" t="n">
-        <v>1010002</v>
+        <v>1020002</v>
       </c>
       <c r="D17" t="n">
-        <v>1010010</v>
+        <v>1020010</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>enemy.blaze-out-of-space.elite.variant.01</t>
+          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C18" t="n">
-        <v>1020002</v>
+        <v>1030002</v>
       </c>
       <c r="D18" t="n">
-        <v>1020010</v>
+        <v>1030010</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
+          <t>enemy.cocolia-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C19" t="n">
-        <v>1030002</v>
+        <v>1040002</v>
       </c>
       <c r="D19" t="n">
-        <v>1030010</v>
+        <v>1040010</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>enemy.cocolia-complete.littleboss.variant.01</t>
+          <t>enemy.gepard-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C20" t="n">
-        <v>1040002</v>
+        <v>1050002</v>
       </c>
       <c r="D20" t="n">
-        <v>1040010</v>
+        <v>1050010</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>enemy.gepard-complete.littleboss.variant.01</t>
+          <t>enemy.ice-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C21" t="n">
-        <v>1050002</v>
+        <v>1060002</v>
       </c>
       <c r="D21" t="n">
-        <v>1050010</v>
+        <v>1060010</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>enemy.ice-out-of-space.elite.variant.01</t>
+          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C22" t="n">
-        <v>1060002</v>
+        <v>1070002</v>
       </c>
       <c r="D22" t="n">
-        <v>1060010</v>
+        <v>1070010</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
+          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C23" t="n">
-        <v>1070002</v>
+        <v>1080002</v>
       </c>
       <c r="D23" t="n">
-        <v>1070010</v>
+        <v>1080010</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
+          <t>enemy.svarog-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C24" t="n">
-        <v>1080002</v>
+        <v>10001</v>
       </c>
       <c r="D24" t="n">
-        <v>1080010</v>
+        <v>1090041</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>enemy.svarog-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>95</v>
+        <v>1090002</v>
       </c>
       <c r="C25" t="n">
-        <v>10001</v>
+        <v>1090022</v>
       </c>
       <c r="D25" t="n">
-        <v>1090041</v>
+        <v>1090042</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
+          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C26" t="n">
-        <v>1090022</v>
+        <v>1090023</v>
       </c>
       <c r="D26" t="n">
-        <v>1090042</v>
+        <v>1090043</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
+          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1090003</v>
+        <v>1090004</v>
       </c>
       <c r="C27" t="n">
-        <v>1090023</v>
+        <v>1090024</v>
       </c>
       <c r="D27" t="n">
-        <v>1090043</v>
+        <v>1090044</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
+          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1090004</v>
+        <v>1090005</v>
       </c>
       <c r="C28" t="n">
-        <v>1090024</v>
+        <v>1090025</v>
       </c>
       <c r="D28" t="n">
-        <v>1090044</v>
+        <v>1090045</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
+          <t>enemy.antibaryon.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1090005</v>
+        <v>1090006</v>
       </c>
       <c r="C29" t="n">
-        <v>1090025</v>
+        <v>1090026</v>
       </c>
       <c r="D29" t="n">
-        <v>1090045</v>
+        <v>1090046</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>enemy.antibaryon.minion.variant.01</t>
+          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C30" t="n">
-        <v>1090026</v>
+        <v>10002</v>
       </c>
       <c r="D30" t="n">
-        <v>1090046</v>
+        <v>1090047</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
+          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C31" t="n">
-        <v>10002</v>
+        <v>1090028</v>
       </c>
       <c r="D31" t="n">
-        <v>1090047</v>
+        <v>1090048</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
+          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1090008</v>
+        <v>1090009</v>
       </c>
       <c r="C32" t="n">
-        <v>1090028</v>
+        <v>1090029</v>
       </c>
       <c r="D32" t="n">
-        <v>1090048</v>
+        <v>1090049</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
+          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1090009</v>
+        <v>1090010</v>
       </c>
       <c r="C33" t="n">
-        <v>1090029</v>
+        <v>1090030</v>
       </c>
       <c r="D33" t="n">
-        <v>1090049</v>
+        <v>1090050</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
+          <t>enemy.automaton-direwolf.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C34" t="n">
-        <v>1090030</v>
+        <v>1090031</v>
       </c>
       <c r="D34" t="n">
-        <v>1090050</v>
+        <v>1090051</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>enemy.automaton-direwolf.elite.variant.01</t>
+          <t>enemy.automaton-grizzly.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090011</v>
+        <v>1090012</v>
       </c>
       <c r="C35" t="n">
-        <v>1090031</v>
+        <v>1090032</v>
       </c>
       <c r="D35" t="n">
-        <v>1090051</v>
+        <v>1090052</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>enemy.automaton-grizzly.elite.variant.01</t>
+          <t>enemy.automaton-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1090012</v>
+        <v>97</v>
       </c>
       <c r="C36" t="n">
-        <v>1090032</v>
+        <v>10003</v>
       </c>
       <c r="D36" t="n">
-        <v>1090052</v>
+        <v>1100041</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>enemy.automaton-hound.minionlv2.variant.01</t>
+          <t>enemy.automaton-spider.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>97</v>
+        <v>1100002</v>
       </c>
       <c r="C37" t="n">
-        <v>10003</v>
+        <v>1100022</v>
       </c>
       <c r="D37" t="n">
-        <v>1100041</v>
+        <v>1100042</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>enemy.automaton-spider.minionlv2.variant.01</t>
+          <t>enemy.baryon.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1100002</v>
+        <v>1100003</v>
       </c>
       <c r="C38" t="n">
-        <v>1100022</v>
+        <v>1100023</v>
       </c>
       <c r="D38" t="n">
-        <v>1100042</v>
+        <v>1100043</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>enemy.baryon.minion.variant.01</t>
+          <t>enemy.cloud-knights-patroller.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1100003</v>
+        <v>1100004</v>
       </c>
       <c r="C39" t="n">
-        <v>1100023</v>
+        <v>1100024</v>
       </c>
       <c r="D39" t="n">
-        <v>1100043</v>
+        <v>1100044</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>enemy.cloud-knights-patroller.minionlv2.variant.01</t>
+          <t>enemy.decaying-shadow.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1100004</v>
+        <v>99</v>
       </c>
       <c r="C40" t="n">
-        <v>1100024</v>
+        <v>10005</v>
       </c>
       <c r="D40" t="n">
-        <v>1100044</v>
+        <v>1100045</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>enemy.decaying-shadow.elite.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>99</v>
+        <v>1100006</v>
       </c>
       <c r="C41" t="n">
-        <v>10005</v>
+        <v>1100026</v>
       </c>
       <c r="D41" t="n">
-        <v>1100045</v>
+        <v>1100046</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-internal-alchemist.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1100006</v>
+        <v>1100007</v>
       </c>
       <c r="C42" t="n">
-        <v>1100026</v>
+        <v>1100027</v>
       </c>
       <c r="D42" t="n">
-        <v>1100046</v>
+        <v>1100047</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-internal-alchemist.minionlv2.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C43" t="n">
-        <v>1100027</v>
+        <v>10006</v>
       </c>
       <c r="D43" t="n">
-        <v>1100047</v>
+        <v>1100048</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-shape-shifter-bug.elite.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C44" t="n">
-        <v>10006</v>
+        <v>1100029</v>
       </c>
       <c r="D44" t="n">
-        <v>1100048</v>
+        <v>1100049</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C45" t="n">
-        <v>1100029</v>
+        <v>1100030</v>
       </c>
       <c r="D45" t="n">
-        <v>1100049</v>
+        <v>1100050</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-beyond-overcooked-bug.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1100010</v>
+        <v>1100011</v>
       </c>
       <c r="C46" t="n">
-        <v>1100030</v>
+        <v>1100031</v>
       </c>
       <c r="D46" t="n">
-        <v>1100050</v>
+        <v>1100051</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-beyond-overcooked.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-birdskull.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1100011</v>
+        <v>1100012</v>
       </c>
       <c r="C47" t="n">
-        <v>1100031</v>
+        <v>1100032</v>
       </c>
       <c r="D47" t="n">
-        <v>1100051</v>
+        <v>1100052</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-birdskull.minion.variant.01</t>
+          <t>enemy.dreamjolt-troupes-bubble-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1100012</v>
+        <v>1110001</v>
       </c>
       <c r="C48" t="n">
-        <v>1100032</v>
+        <v>1110021</v>
       </c>
       <c r="D48" t="n">
-        <v>1100052</v>
+        <v>1110041</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-bubble-hound.minionlv2.variant.01</t>
+          <t>enemy.dreamjolt-troupes-mr-domescreen.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1110001</v>
+        <v>1110002</v>
       </c>
       <c r="C49" t="n">
-        <v>1110021</v>
+        <v>1110022</v>
       </c>
       <c r="D49" t="n">
-        <v>1110041</v>
+        <v>1110042</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-mr-domescreen.minionlv2.variant.01</t>
+          <t>enemy.dreamjolt-troupes-spring-loader.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1110002</v>
+        <v>1110003</v>
       </c>
       <c r="C50" t="n">
-        <v>1110022</v>
+        <v>1110023</v>
       </c>
       <c r="D50" t="n">
-        <v>1110042</v>
+        <v>1110043</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-spring-loader.minion.variant.01</t>
+          <t>enemy.dreamjolt-troupes-sweet-gorilla-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1110003</v>
+        <v>1110004</v>
       </c>
       <c r="C51" t="n">
-        <v>1110023</v>
+        <v>1110024</v>
       </c>
       <c r="D51" t="n">
-        <v>1110043</v>
+        <v>1110044</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-sweet-gorilla-bug.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-sweet-gorilla.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1110004</v>
+        <v>1110005</v>
       </c>
       <c r="C52" t="n">
-        <v>1110024</v>
+        <v>1110025</v>
       </c>
       <c r="D52" t="n">
-        <v>1110044</v>
+        <v>1110045</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-sweet-gorilla.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-winder-goon.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1110005</v>
+        <v>1110006</v>
       </c>
       <c r="C53" t="n">
-        <v>1110025</v>
+        <v>1110026</v>
       </c>
       <c r="D53" t="n">
-        <v>1110045</v>
+        <v>1110046</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-winder-goon.minionlv2.variant.01</t>
+          <t>enemy.entranced-ingenium-golden-cloud-toad.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1110006</v>
+        <v>102</v>
       </c>
       <c r="C54" t="n">
-        <v>1110026</v>
+        <v>10008</v>
       </c>
       <c r="D54" t="n">
-        <v>1110046</v>
+        <v>1110047</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-golden-cloud-toad.minion.variant.01</t>
+          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>102</v>
+        <v>1110008</v>
       </c>
       <c r="C55" t="n">
-        <v>10008</v>
+        <v>1110028</v>
       </c>
       <c r="D55" t="n">
-        <v>1110047</v>
+        <v>1110048</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
+          <t>enemy.entranced-ingenium-obedient-dracolion.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1110008</v>
+        <v>1110009</v>
       </c>
       <c r="C56" t="n">
-        <v>1110028</v>
+        <v>1110029</v>
       </c>
       <c r="D56" t="n">
-        <v>1110048</v>
+        <v>1110049</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-obedient-dracolion.minion.variant.01</t>
+          <t>enemy.everwinter-shadewalker.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1110009</v>
+        <v>103</v>
       </c>
       <c r="C57" t="n">
-        <v>1110029</v>
+        <v>10009</v>
       </c>
       <c r="D57" t="n">
-        <v>1110049</v>
+        <v>1110050</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>enemy.everwinter-shadewalker.minionlv2.variant.01</t>
+          <t>enemy.flamespawn.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>103</v>
+        <v>1110011</v>
       </c>
       <c r="C58" t="n">
-        <v>10009</v>
+        <v>1110031</v>
       </c>
       <c r="D58" t="n">
-        <v>1110050</v>
+        <v>1110051</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>enemy.flamespawn.minion.variant.01</t>
+          <t>enemy.frigid-prowler.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1110011</v>
+        <v>104</v>
       </c>
       <c r="C59" t="n">
-        <v>1110031</v>
+        <v>10010</v>
       </c>
       <c r="D59" t="n">
-        <v>1110051</v>
+        <v>1110052</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>enemy.frigid-prowler.elite.variant.01</t>
+          <t>enemy.frostspawn.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>104</v>
+        <v>1120001</v>
       </c>
       <c r="C60" t="n">
-        <v>10010</v>
+        <v>1120021</v>
       </c>
       <c r="D60" t="n">
-        <v>1110052</v>
+        <v>1120041</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>enemy.frostspawn.minion.variant.01</t>
+          <t>enemy.grunt-field-personnel.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1120001</v>
+        <v>1120002</v>
       </c>
       <c r="C61" t="n">
-        <v>1120021</v>
+        <v>1120022</v>
       </c>
       <c r="D61" t="n">
-        <v>1120041</v>
+        <v>1120042</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>enemy.grunt-field-personnel.minionlv2.variant.01</t>
+          <t>enemy.grunt-security-personnel.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1120002</v>
+        <v>1120003</v>
       </c>
       <c r="C62" t="n">
-        <v>1120022</v>
+        <v>1120023</v>
       </c>
       <c r="D62" t="n">
-        <v>1120042</v>
+        <v>1120043</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>enemy.grunt-security-personnel.minionlv2.variant.01</t>
+          <t>enemy.guardian-shadow.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1120003</v>
+        <v>1120004</v>
       </c>
       <c r="C63" t="n">
-        <v>1120023</v>
+        <v>1120024</v>
       </c>
       <c r="D63" t="n">
-        <v>1120043</v>
+        <v>1120044</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>enemy.guardian-shadow.elite.variant.01</t>
+          <t>enemy.imaginary-weaver.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1120004</v>
+        <v>106</v>
       </c>
       <c r="C64" t="n">
-        <v>1120024</v>
+        <v>10012</v>
       </c>
       <c r="D64" t="n">
-        <v>1120044</v>
+        <v>1120045</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>enemy.imaginary-weaver.minionlv2.variant.01</t>
+          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>106</v>
+        <v>1120006</v>
       </c>
       <c r="C65" t="n">
-        <v>10012</v>
+        <v>1120026</v>
       </c>
       <c r="D65" t="n">
-        <v>1120045</v>
+        <v>1120046</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
+          <t>enemy.juvenile-sting.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1120006</v>
+        <v>1120007</v>
       </c>
       <c r="C66" t="n">
-        <v>1120026</v>
+        <v>1120027</v>
       </c>
       <c r="D66" t="n">
-        <v>1120046</v>
+        <v>1120047</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>enemy.juvenile-sting.minionlv2.variant.01</t>
+          <t>enemy.lesser-sting.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1120007</v>
+        <v>107</v>
       </c>
       <c r="C67" t="n">
-        <v>1120027</v>
+        <v>10013</v>
       </c>
       <c r="D67" t="n">
-        <v>1120047</v>
+        <v>1120048</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>enemy.lesser-sting.minionlv2.variant.01</t>
+          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C68" t="n">
-        <v>10013</v>
+        <v>10014</v>
       </c>
       <c r="D68" t="n">
-        <v>1120048</v>
+        <v>1120049</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
+          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>108</v>
+        <v>1120010</v>
       </c>
       <c r="C69" t="n">
-        <v>10014</v>
+        <v>1120030</v>
       </c>
       <c r="D69" t="n">
-        <v>1120049</v>
+        <v>1120050</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
+          <t>enemy.mask-of-no-thought.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1120010</v>
+        <v>1120011</v>
       </c>
       <c r="C70" t="n">
-        <v>1120030</v>
+        <v>1120031</v>
       </c>
       <c r="D70" t="n">
-        <v>1120050</v>
+        <v>1120051</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>enemy.mask-of-no-thought.minion.variant.01</t>
+          <t>enemy.memory-zone-meme-allseer.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1120011</v>
+        <v>1120012</v>
       </c>
       <c r="C71" t="n">
-        <v>1120031</v>
+        <v>1120032</v>
       </c>
       <c r="D71" t="n">
-        <v>1120051</v>
+        <v>1120052</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-allseer.minion.variant.01</t>
+          <t>enemy.memory-zone-meme-heartbreaker.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1120012</v>
+        <v>1130001</v>
       </c>
       <c r="C72" t="n">
-        <v>1120032</v>
+        <v>1130021</v>
       </c>
       <c r="D72" t="n">
-        <v>1120052</v>
+        <v>1130041</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-heartbreaker.minionlv2.variant.01</t>
+          <t>enemy.memory-zone-meme-shell-of-faded-rage.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1130001</v>
+        <v>1130002</v>
       </c>
       <c r="C73" t="n">
-        <v>1130021</v>
+        <v>1130022</v>
       </c>
       <c r="D73" t="n">
-        <v>1130041</v>
+        <v>1130042</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-shell-of-faded-rage.elite.variant.01</t>
+          <t>enemy.memory-zone-meme-something-in-the-mirror.minionlv2.variant.02</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1130002</v>
+        <v>1130003</v>
       </c>
       <c r="C74" t="n">
-        <v>1130022</v>
+        <v>1130023</v>
       </c>
       <c r="D74" t="n">
-        <v>1130042</v>
+        <v>1130043</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-something-in-the-mirror.minionlv2.variant.02</t>
+          <t>enemy.searing-prowler.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1130003</v>
+        <v>1130004</v>
       </c>
       <c r="C75" t="n">
-        <v>1130023</v>
+        <v>1130024</v>
       </c>
       <c r="D75" t="n">
-        <v>1130043</v>
+        <v>1130044</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>enemy.searing-prowler.elite.variant.01</t>
+          <t>enemy.senior-staff-team-leader-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1130004</v>
+        <v>1130005</v>
       </c>
       <c r="C76" t="n">
-        <v>1130024</v>
+        <v>1130025</v>
       </c>
       <c r="D76" t="n">
-        <v>1130044</v>
+        <v>1130045</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>enemy.senior-staff-team-leader-bug.elite.variant.01</t>
+          <t>enemy.senior-staff-team-leader.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1130005</v>
+        <v>1130006</v>
       </c>
       <c r="C77" t="n">
-        <v>1130025</v>
+        <v>1130026</v>
       </c>
       <c r="D77" t="n">
-        <v>1130045</v>
+        <v>1130046</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>enemy.senior-staff-team-leader.elite.variant.01</t>
+          <t>enemy.silvermane-cannoneer.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1130006</v>
+        <v>1130007</v>
       </c>
       <c r="C78" t="n">
-        <v>1130026</v>
+        <v>1130027</v>
       </c>
       <c r="D78" t="n">
-        <v>1130046</v>
+        <v>1130047</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>enemy.silvermane-cannoneer.minionlv2.variant.01</t>
+          <t>enemy.silvermane-gunner.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1130007</v>
+        <v>1130008</v>
       </c>
       <c r="C79" t="n">
-        <v>1130027</v>
+        <v>1130028</v>
       </c>
       <c r="D79" t="n">
-        <v>1130047</v>
+        <v>1130048</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>enemy.silvermane-gunner.minionlv2.variant.01</t>
+          <t>enemy.silvermane-lieutenant-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1130008</v>
+        <v>1130009</v>
       </c>
       <c r="C80" t="n">
-        <v>1130028</v>
+        <v>1130029</v>
       </c>
       <c r="D80" t="n">
-        <v>1130048</v>
+        <v>1130049</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>enemy.silvermane-lieutenant-bug.elite.variant.01</t>
+          <t>enemy.silvermane-soldier.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1130009</v>
+        <v>1130010</v>
       </c>
       <c r="C81" t="n">
-        <v>1130029</v>
+        <v>1130030</v>
       </c>
       <c r="D81" t="n">
-        <v>1130049</v>
+        <v>1130050</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>enemy.silvermane-soldier.minionlv2.variant.01</t>
+          <t>enemy.stormbringer-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1130010</v>
+        <v>1130011</v>
       </c>
       <c r="C82" t="n">
-        <v>1130030</v>
+        <v>1130031</v>
       </c>
       <c r="D82" t="n">
-        <v>1130050</v>
+        <v>1130051</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>enemy.stormbringer-bug.elite.variant.01</t>
+          <t>enemy.stormbringer.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1130011</v>
+        <v>1130012</v>
       </c>
       <c r="C83" t="n">
-        <v>1130031</v>
+        <v>1130032</v>
       </c>
       <c r="D83" t="n">
-        <v>1130051</v>
+        <v>1130052</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>enemy.stormbringer.elite.variant.01</t>
+          <t>enemy.the-ascended.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1130012</v>
+        <v>1140001</v>
       </c>
       <c r="C84" t="n">
-        <v>1130032</v>
+        <v>1140021</v>
       </c>
       <c r="D84" t="n">
-        <v>1130052</v>
+        <v>1140041</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>enemy.the-ascended.elite.variant.01</t>
+          <t>enemy.thunderspawn.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1140022</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1140042</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>enemy.trotter-of-abundance.minionlv2.02.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1140023</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1140043</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>enemy.trotter-of-abundance.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1140024</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1140044</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>enemy.trotter-of-destruction.minionlv2.02.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1140025</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1140045</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>enemy.trotter-of-destruction.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1140026</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1140046</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>enemy.trotter-of-preservation.minionlv2.03.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1140027</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1140047</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>enemy.trotter-of-preservation.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1140028</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1140048</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>enemy.vagrant.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1140029</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1140049</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>enemy.voidranger-distorter.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1140030</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1140050</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>enemy.voidranger-eliminator.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>110</v>
+      </c>
+      <c r="C94" t="n">
+        <v>10016</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1140051</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1140032</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>enemy.voidranger-trampler-bug.elite.variant.01</t>
         </is>
       </c>
     </row>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,1361 +649,1393 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C11" t="n">
-        <v>10017</v>
+        <v>10004</v>
       </c>
       <c r="D11" t="n">
-        <v>13017</v>
+        <v>13004</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>enemy.voidranger-trampler.elite.variant.01</t>
+          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C12" t="n">
-        <v>10004</v>
+        <v>980002</v>
       </c>
       <c r="D12" t="n">
-        <v>13004</v>
+        <v>980010</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
+          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C13" t="n">
-        <v>980002</v>
+        <v>990002</v>
       </c>
       <c r="D13" t="n">
-        <v>980010</v>
+        <v>990010</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
+          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C14" t="n">
-        <v>990002</v>
+        <v>1000002</v>
       </c>
       <c r="D14" t="n">
-        <v>990010</v>
+        <v>1000010</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
+          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C15" t="n">
-        <v>1000002</v>
+        <v>1010002</v>
       </c>
       <c r="D15" t="n">
-        <v>1000010</v>
+        <v>1010010</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
+          <t>enemy.blaze-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C16" t="n">
-        <v>1010002</v>
+        <v>1020002</v>
       </c>
       <c r="D16" t="n">
-        <v>1010010</v>
+        <v>1020010</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>enemy.blaze-out-of-space.elite.variant.01</t>
+          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C17" t="n">
-        <v>1020002</v>
+        <v>1030002</v>
       </c>
       <c r="D17" t="n">
-        <v>1020010</v>
+        <v>1030010</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
+          <t>enemy.cocolia-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C18" t="n">
-        <v>1030002</v>
+        <v>1040002</v>
       </c>
       <c r="D18" t="n">
-        <v>1030010</v>
+        <v>1040010</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>enemy.cocolia-complete.littleboss.variant.01</t>
+          <t>enemy.gepard-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C19" t="n">
-        <v>1040002</v>
+        <v>1050002</v>
       </c>
       <c r="D19" t="n">
-        <v>1040010</v>
+        <v>1050010</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>enemy.gepard-complete.littleboss.variant.01</t>
+          <t>enemy.ice-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C20" t="n">
-        <v>1050002</v>
+        <v>1060002</v>
       </c>
       <c r="D20" t="n">
-        <v>1050010</v>
+        <v>1060010</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>enemy.ice-out-of-space.elite.variant.01</t>
+          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C21" t="n">
-        <v>1060002</v>
+        <v>1070002</v>
       </c>
       <c r="D21" t="n">
-        <v>1060010</v>
+        <v>1070010</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
+          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C22" t="n">
-        <v>1070002</v>
+        <v>1080002</v>
       </c>
       <c r="D22" t="n">
-        <v>1070010</v>
+        <v>1080010</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
+          <t>enemy.svarog-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C23" t="n">
-        <v>1080002</v>
+        <v>10001</v>
       </c>
       <c r="D23" t="n">
-        <v>1080010</v>
+        <v>1090041</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>enemy.svarog-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>95</v>
+        <v>1090002</v>
       </c>
       <c r="C24" t="n">
-        <v>10001</v>
+        <v>1090022</v>
       </c>
       <c r="D24" t="n">
-        <v>1090041</v>
+        <v>1090042</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
+          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C25" t="n">
-        <v>1090022</v>
+        <v>1090023</v>
       </c>
       <c r="D25" t="n">
-        <v>1090042</v>
+        <v>1090043</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
+          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1090003</v>
+        <v>1090004</v>
       </c>
       <c r="C26" t="n">
-        <v>1090023</v>
+        <v>1090024</v>
       </c>
       <c r="D26" t="n">
-        <v>1090043</v>
+        <v>1090044</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
+          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1090004</v>
+        <v>1090005</v>
       </c>
       <c r="C27" t="n">
-        <v>1090024</v>
+        <v>1090025</v>
       </c>
       <c r="D27" t="n">
-        <v>1090044</v>
+        <v>1090045</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
+          <t>enemy.antibaryon.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1090005</v>
+        <v>1090006</v>
       </c>
       <c r="C28" t="n">
-        <v>1090025</v>
+        <v>1090026</v>
       </c>
       <c r="D28" t="n">
-        <v>1090045</v>
+        <v>1090046</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>enemy.antibaryon.minion.variant.01</t>
+          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C29" t="n">
-        <v>1090026</v>
+        <v>10002</v>
       </c>
       <c r="D29" t="n">
-        <v>1090046</v>
+        <v>1090047</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
+          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C30" t="n">
-        <v>10002</v>
+        <v>1090028</v>
       </c>
       <c r="D30" t="n">
-        <v>1090047</v>
+        <v>1090048</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
+          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1090008</v>
+        <v>1090009</v>
       </c>
       <c r="C31" t="n">
-        <v>1090028</v>
+        <v>1090029</v>
       </c>
       <c r="D31" t="n">
-        <v>1090048</v>
+        <v>1090049</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
+          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1090009</v>
+        <v>1090010</v>
       </c>
       <c r="C32" t="n">
-        <v>1090029</v>
+        <v>1090030</v>
       </c>
       <c r="D32" t="n">
-        <v>1090049</v>
+        <v>1090050</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
+          <t>enemy.automaton-direwolf.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C33" t="n">
-        <v>1090030</v>
+        <v>1090031</v>
       </c>
       <c r="D33" t="n">
-        <v>1090050</v>
+        <v>1090051</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>enemy.automaton-direwolf.elite.variant.01</t>
+          <t>enemy.automaton-grizzly.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1090011</v>
+        <v>1090012</v>
       </c>
       <c r="C34" t="n">
-        <v>1090031</v>
+        <v>1090032</v>
       </c>
       <c r="D34" t="n">
-        <v>1090051</v>
+        <v>1090052</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>enemy.automaton-grizzly.elite.variant.01</t>
+          <t>enemy.automaton-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090012</v>
+        <v>97</v>
       </c>
       <c r="C35" t="n">
-        <v>1090032</v>
+        <v>10003</v>
       </c>
       <c r="D35" t="n">
-        <v>1090052</v>
+        <v>1100041</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>enemy.automaton-hound.minionlv2.variant.01</t>
+          <t>enemy.automaton-spider.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>97</v>
+        <v>1100002</v>
       </c>
       <c r="C36" t="n">
-        <v>10003</v>
+        <v>1100022</v>
       </c>
       <c r="D36" t="n">
-        <v>1100041</v>
+        <v>1100042</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>enemy.automaton-spider.minionlv2.variant.01</t>
+          <t>enemy.baryon.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1100002</v>
+        <v>1100003</v>
       </c>
       <c r="C37" t="n">
-        <v>1100022</v>
+        <v>1100023</v>
       </c>
       <c r="D37" t="n">
-        <v>1100042</v>
+        <v>1100043</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>enemy.baryon.minion.variant.01</t>
+          <t>enemy.cloud-knights-patroller.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1100003</v>
+        <v>1100004</v>
       </c>
       <c r="C38" t="n">
-        <v>1100023</v>
+        <v>1100024</v>
       </c>
       <c r="D38" t="n">
-        <v>1100043</v>
+        <v>1100044</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>enemy.cloud-knights-patroller.minionlv2.variant.01</t>
+          <t>enemy.decaying-shadow.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1100004</v>
+        <v>99</v>
       </c>
       <c r="C39" t="n">
-        <v>1100024</v>
+        <v>10005</v>
       </c>
       <c r="D39" t="n">
-        <v>1100044</v>
+        <v>1100045</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>enemy.decaying-shadow.elite.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>99</v>
+        <v>1100006</v>
       </c>
       <c r="C40" t="n">
-        <v>10005</v>
+        <v>1100026</v>
       </c>
       <c r="D40" t="n">
-        <v>1100045</v>
+        <v>1100046</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-internal-alchemist.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1100006</v>
+        <v>1100007</v>
       </c>
       <c r="C41" t="n">
-        <v>1100026</v>
+        <v>1100027</v>
       </c>
       <c r="D41" t="n">
-        <v>1100046</v>
+        <v>1100047</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-internal-alchemist.minionlv2.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C42" t="n">
-        <v>1100027</v>
+        <v>10006</v>
       </c>
       <c r="D42" t="n">
-        <v>1100047</v>
+        <v>1100048</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-shape-shifter-bug.elite.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C43" t="n">
-        <v>10006</v>
+        <v>1100029</v>
       </c>
       <c r="D43" t="n">
-        <v>1100048</v>
+        <v>1100049</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1100009</v>
+        <v>1100010</v>
       </c>
       <c r="C44" t="n">
-        <v>1100029</v>
+        <v>1100030</v>
       </c>
       <c r="D44" t="n">
-        <v>1100049</v>
+        <v>1100050</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-beyond-overcooked-bug.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1100010</v>
+        <v>1100011</v>
       </c>
       <c r="C45" t="n">
-        <v>1100030</v>
+        <v>1100031</v>
       </c>
       <c r="D45" t="n">
-        <v>1100050</v>
+        <v>1100051</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-beyond-overcooked.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-birdskull.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1100011</v>
+        <v>1100012</v>
       </c>
       <c r="C46" t="n">
-        <v>1100031</v>
+        <v>1100032</v>
       </c>
       <c r="D46" t="n">
-        <v>1100051</v>
+        <v>1100052</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-birdskull.minion.variant.01</t>
+          <t>enemy.dreamjolt-troupes-bubble-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1100012</v>
+        <v>1110001</v>
       </c>
       <c r="C47" t="n">
-        <v>1100032</v>
+        <v>1110021</v>
       </c>
       <c r="D47" t="n">
-        <v>1100052</v>
+        <v>1110041</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-bubble-hound.minionlv2.variant.01</t>
+          <t>enemy.dreamjolt-troupes-mr-domescreen.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1110001</v>
+        <v>1110002</v>
       </c>
       <c r="C48" t="n">
-        <v>1110021</v>
+        <v>1110022</v>
       </c>
       <c r="D48" t="n">
-        <v>1110041</v>
+        <v>1110042</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-mr-domescreen.minionlv2.variant.01</t>
+          <t>enemy.dreamjolt-troupes-spring-loader.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1110002</v>
+        <v>1110003</v>
       </c>
       <c r="C49" t="n">
-        <v>1110022</v>
+        <v>1110023</v>
       </c>
       <c r="D49" t="n">
-        <v>1110042</v>
+        <v>1110043</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-spring-loader.minion.variant.01</t>
+          <t>enemy.dreamjolt-troupes-sweet-gorilla-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1110003</v>
+        <v>1110004</v>
       </c>
       <c r="C50" t="n">
-        <v>1110023</v>
+        <v>1110024</v>
       </c>
       <c r="D50" t="n">
-        <v>1110043</v>
+        <v>1110044</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-sweet-gorilla-bug.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-sweet-gorilla.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1110004</v>
+        <v>1110005</v>
       </c>
       <c r="C51" t="n">
-        <v>1110024</v>
+        <v>1110025</v>
       </c>
       <c r="D51" t="n">
-        <v>1110044</v>
+        <v>1110045</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-sweet-gorilla.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-winder-goon.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1110005</v>
+        <v>1110006</v>
       </c>
       <c r="C52" t="n">
-        <v>1110025</v>
+        <v>1110026</v>
       </c>
       <c r="D52" t="n">
-        <v>1110045</v>
+        <v>1110046</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-winder-goon.minionlv2.variant.01</t>
+          <t>enemy.entranced-ingenium-golden-cloud-toad.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1110006</v>
+        <v>102</v>
       </c>
       <c r="C53" t="n">
-        <v>1110026</v>
+        <v>10008</v>
       </c>
       <c r="D53" t="n">
-        <v>1110046</v>
+        <v>1110047</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-golden-cloud-toad.minion.variant.01</t>
+          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>102</v>
+        <v>1110008</v>
       </c>
       <c r="C54" t="n">
-        <v>10008</v>
+        <v>1110028</v>
       </c>
       <c r="D54" t="n">
-        <v>1110047</v>
+        <v>1110048</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
+          <t>enemy.entranced-ingenium-obedient-dracolion.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1110008</v>
+        <v>1110009</v>
       </c>
       <c r="C55" t="n">
-        <v>1110028</v>
+        <v>1110029</v>
       </c>
       <c r="D55" t="n">
-        <v>1110048</v>
+        <v>1110049</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-obedient-dracolion.minion.variant.01</t>
+          <t>enemy.everwinter-shadewalker.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1110009</v>
+        <v>103</v>
       </c>
       <c r="C56" t="n">
-        <v>1110029</v>
+        <v>10009</v>
       </c>
       <c r="D56" t="n">
-        <v>1110049</v>
+        <v>1110050</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>enemy.everwinter-shadewalker.minionlv2.variant.01</t>
+          <t>enemy.flamespawn.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>103</v>
+        <v>1110011</v>
       </c>
       <c r="C57" t="n">
-        <v>10009</v>
+        <v>1110031</v>
       </c>
       <c r="D57" t="n">
-        <v>1110050</v>
+        <v>1110051</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>enemy.flamespawn.minion.variant.01</t>
+          <t>enemy.frigid-prowler.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1110011</v>
+        <v>104</v>
       </c>
       <c r="C58" t="n">
-        <v>1110031</v>
+        <v>10010</v>
       </c>
       <c r="D58" t="n">
-        <v>1110051</v>
+        <v>1110052</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>enemy.frigid-prowler.elite.variant.01</t>
+          <t>enemy.frostspawn.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>104</v>
+        <v>1120001</v>
       </c>
       <c r="C59" t="n">
-        <v>10010</v>
+        <v>1120021</v>
       </c>
       <c r="D59" t="n">
-        <v>1110052</v>
+        <v>1120041</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>enemy.frostspawn.minion.variant.01</t>
+          <t>enemy.grunt-field-personnel.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1120001</v>
+        <v>1120002</v>
       </c>
       <c r="C60" t="n">
-        <v>1120021</v>
+        <v>1120022</v>
       </c>
       <c r="D60" t="n">
-        <v>1120041</v>
+        <v>1120042</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>enemy.grunt-field-personnel.minionlv2.variant.01</t>
+          <t>enemy.grunt-security-personnel.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1120002</v>
+        <v>1120003</v>
       </c>
       <c r="C61" t="n">
-        <v>1120022</v>
+        <v>1120023</v>
       </c>
       <c r="D61" t="n">
-        <v>1120042</v>
+        <v>1120043</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>enemy.grunt-security-personnel.minionlv2.variant.01</t>
+          <t>enemy.guardian-shadow.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1120003</v>
+        <v>1120004</v>
       </c>
       <c r="C62" t="n">
-        <v>1120023</v>
+        <v>1120024</v>
       </c>
       <c r="D62" t="n">
-        <v>1120043</v>
+        <v>1120044</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>enemy.guardian-shadow.elite.variant.01</t>
+          <t>enemy.imaginary-weaver.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1120004</v>
+        <v>106</v>
       </c>
       <c r="C63" t="n">
-        <v>1120024</v>
+        <v>10012</v>
       </c>
       <c r="D63" t="n">
-        <v>1120044</v>
+        <v>1120045</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>enemy.imaginary-weaver.minionlv2.variant.01</t>
+          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>106</v>
+        <v>1120006</v>
       </c>
       <c r="C64" t="n">
-        <v>10012</v>
+        <v>1120026</v>
       </c>
       <c r="D64" t="n">
-        <v>1120045</v>
+        <v>1120046</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
+          <t>enemy.juvenile-sting.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1120006</v>
+        <v>1120007</v>
       </c>
       <c r="C65" t="n">
-        <v>1120026</v>
+        <v>1120027</v>
       </c>
       <c r="D65" t="n">
-        <v>1120046</v>
+        <v>1120047</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>enemy.juvenile-sting.minionlv2.variant.01</t>
+          <t>enemy.lesser-sting.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1120007</v>
+        <v>107</v>
       </c>
       <c r="C66" t="n">
-        <v>1120027</v>
+        <v>10013</v>
       </c>
       <c r="D66" t="n">
-        <v>1120047</v>
+        <v>1120048</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>enemy.lesser-sting.minionlv2.variant.01</t>
+          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C67" t="n">
-        <v>10013</v>
+        <v>10014</v>
       </c>
       <c r="D67" t="n">
-        <v>1120048</v>
+        <v>1120049</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
+          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>108</v>
+        <v>1120010</v>
       </c>
       <c r="C68" t="n">
-        <v>10014</v>
+        <v>1120030</v>
       </c>
       <c r="D68" t="n">
-        <v>1120049</v>
+        <v>1120050</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
+          <t>enemy.mask-of-no-thought.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1120010</v>
+        <v>1120011</v>
       </c>
       <c r="C69" t="n">
-        <v>1120030</v>
+        <v>1120031</v>
       </c>
       <c r="D69" t="n">
-        <v>1120050</v>
+        <v>1120051</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>enemy.mask-of-no-thought.minion.variant.01</t>
+          <t>enemy.memory-zone-meme-allseer.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1120011</v>
+        <v>1120012</v>
       </c>
       <c r="C70" t="n">
-        <v>1120031</v>
+        <v>1120032</v>
       </c>
       <c r="D70" t="n">
-        <v>1120051</v>
+        <v>1120052</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-allseer.minion.variant.01</t>
+          <t>enemy.memory-zone-meme-heartbreaker.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1120012</v>
+        <v>1130001</v>
       </c>
       <c r="C71" t="n">
-        <v>1120032</v>
+        <v>1130021</v>
       </c>
       <c r="D71" t="n">
-        <v>1120052</v>
+        <v>1130041</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-heartbreaker.minionlv2.variant.01</t>
+          <t>enemy.memory-zone-meme-shell-of-faded-rage.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1130001</v>
+        <v>1130002</v>
       </c>
       <c r="C72" t="n">
-        <v>1130021</v>
+        <v>1130022</v>
       </c>
       <c r="D72" t="n">
-        <v>1130041</v>
+        <v>1130042</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-shell-of-faded-rage.elite.variant.01</t>
+          <t>enemy.memory-zone-meme-something-in-the-mirror.minionlv2.variant.02</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1130002</v>
+        <v>1130003</v>
       </c>
       <c r="C73" t="n">
-        <v>1130022</v>
+        <v>1130023</v>
       </c>
       <c r="D73" t="n">
-        <v>1130042</v>
+        <v>1130043</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-something-in-the-mirror.minionlv2.variant.02</t>
+          <t>enemy.searing-prowler.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1130003</v>
+        <v>1130004</v>
       </c>
       <c r="C74" t="n">
-        <v>1130023</v>
+        <v>1130024</v>
       </c>
       <c r="D74" t="n">
-        <v>1130043</v>
+        <v>1130044</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>enemy.searing-prowler.elite.variant.01</t>
+          <t>enemy.senior-staff-team-leader-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1130004</v>
+        <v>1130005</v>
       </c>
       <c r="C75" t="n">
-        <v>1130024</v>
+        <v>1130025</v>
       </c>
       <c r="D75" t="n">
-        <v>1130044</v>
+        <v>1130045</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>enemy.senior-staff-team-leader-bug.elite.variant.01</t>
+          <t>enemy.senior-staff-team-leader.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1130005</v>
+        <v>1130006</v>
       </c>
       <c r="C76" t="n">
-        <v>1130025</v>
+        <v>1130026</v>
       </c>
       <c r="D76" t="n">
-        <v>1130045</v>
+        <v>1130046</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>enemy.senior-staff-team-leader.elite.variant.01</t>
+          <t>enemy.silvermane-cannoneer.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1130006</v>
+        <v>1130007</v>
       </c>
       <c r="C77" t="n">
-        <v>1130026</v>
+        <v>1130027</v>
       </c>
       <c r="D77" t="n">
-        <v>1130046</v>
+        <v>1130047</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>enemy.silvermane-cannoneer.minionlv2.variant.01</t>
+          <t>enemy.silvermane-gunner.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1130007</v>
+        <v>1130008</v>
       </c>
       <c r="C78" t="n">
-        <v>1130027</v>
+        <v>1130028</v>
       </c>
       <c r="D78" t="n">
-        <v>1130047</v>
+        <v>1130048</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>enemy.silvermane-gunner.minionlv2.variant.01</t>
+          <t>enemy.silvermane-lieutenant-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1130008</v>
+        <v>1130009</v>
       </c>
       <c r="C79" t="n">
-        <v>1130028</v>
+        <v>1130029</v>
       </c>
       <c r="D79" t="n">
-        <v>1130048</v>
+        <v>1130049</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>enemy.silvermane-lieutenant-bug.elite.variant.01</t>
+          <t>enemy.silvermane-soldier.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1130009</v>
+        <v>1130010</v>
       </c>
       <c r="C80" t="n">
-        <v>1130029</v>
+        <v>1130030</v>
       </c>
       <c r="D80" t="n">
-        <v>1130049</v>
+        <v>1130050</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>enemy.silvermane-soldier.minionlv2.variant.01</t>
+          <t>enemy.stormbringer-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1130010</v>
+        <v>1130011</v>
       </c>
       <c r="C81" t="n">
-        <v>1130030</v>
+        <v>1130031</v>
       </c>
       <c r="D81" t="n">
-        <v>1130050</v>
+        <v>1130051</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>enemy.stormbringer-bug.elite.variant.01</t>
+          <t>enemy.stormbringer.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1130011</v>
+        <v>1130012</v>
       </c>
       <c r="C82" t="n">
-        <v>1130031</v>
+        <v>1130032</v>
       </c>
       <c r="D82" t="n">
-        <v>1130051</v>
+        <v>1130052</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>enemy.stormbringer.elite.variant.01</t>
+          <t>enemy.the-ascended.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1130012</v>
+        <v>1140001</v>
       </c>
       <c r="C83" t="n">
-        <v>1130032</v>
+        <v>1140021</v>
       </c>
       <c r="D83" t="n">
-        <v>1130052</v>
+        <v>1140041</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>enemy.the-ascended.elite.variant.01</t>
+          <t>enemy.thunderspawn.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1140001</v>
+        <v>1140002</v>
       </c>
       <c r="C84" t="n">
-        <v>1140021</v>
+        <v>1140022</v>
       </c>
       <c r="D84" t="n">
-        <v>1140041</v>
+        <v>1140042</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>enemy.thunderspawn.minion.variant.01</t>
+          <t>enemy.trotter-of-abundance.minionlv2.02.variant.01</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1140002</v>
+        <v>1140003</v>
       </c>
       <c r="C85" t="n">
-        <v>1140022</v>
+        <v>1140023</v>
       </c>
       <c r="D85" t="n">
-        <v>1140042</v>
+        <v>1140043</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>enemy.trotter-of-abundance.minionlv2.02.variant.01</t>
+          <t>enemy.trotter-of-abundance.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1140003</v>
+        <v>1140004</v>
       </c>
       <c r="C86" t="n">
-        <v>1140023</v>
+        <v>1140024</v>
       </c>
       <c r="D86" t="n">
-        <v>1140043</v>
+        <v>1140044</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>enemy.trotter-of-abundance.minionlv2.variant.01</t>
+          <t>enemy.trotter-of-destruction.minionlv2.02.variant.01</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1140004</v>
+        <v>1140005</v>
       </c>
       <c r="C87" t="n">
-        <v>1140024</v>
+        <v>1140025</v>
       </c>
       <c r="D87" t="n">
-        <v>1140044</v>
+        <v>1140045</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>enemy.trotter-of-destruction.minionlv2.02.variant.01</t>
+          <t>enemy.trotter-of-destruction.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1140005</v>
+        <v>1140006</v>
       </c>
       <c r="C88" t="n">
-        <v>1140025</v>
+        <v>1140026</v>
       </c>
       <c r="D88" t="n">
-        <v>1140045</v>
+        <v>1140046</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>enemy.trotter-of-destruction.minionlv2.variant.01</t>
+          <t>enemy.trotter-of-preservation.minionlv2.03.variant.01</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1140006</v>
+        <v>1140007</v>
       </c>
       <c r="C89" t="n">
-        <v>1140026</v>
+        <v>1140027</v>
       </c>
       <c r="D89" t="n">
-        <v>1140046</v>
+        <v>1140047</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>enemy.trotter-of-preservation.minionlv2.03.variant.01</t>
+          <t>enemy.trotter-of-preservation.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1140007</v>
+        <v>1140008</v>
       </c>
       <c r="C90" t="n">
-        <v>1140027</v>
+        <v>1140028</v>
       </c>
       <c r="D90" t="n">
-        <v>1140047</v>
+        <v>1140048</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>enemy.trotter-of-preservation.minionlv2.variant.01</t>
+          <t>enemy.vagrant.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1140008</v>
+        <v>1140009</v>
       </c>
       <c r="C91" t="n">
-        <v>1140028</v>
+        <v>1140029</v>
       </c>
       <c r="D91" t="n">
-        <v>1140048</v>
+        <v>1140049</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>enemy.vagrant.minionlv2.variant.01</t>
+          <t>enemy.voidranger-distorter.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1140009</v>
+        <v>1140010</v>
       </c>
       <c r="C92" t="n">
-        <v>1140029</v>
+        <v>1140030</v>
       </c>
       <c r="D92" t="n">
-        <v>1140049</v>
+        <v>1140050</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>enemy.voidranger-distorter.minionlv2.variant.01</t>
+          <t>enemy.voidranger-eliminator.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1140010</v>
+        <v>110</v>
       </c>
       <c r="C93" t="n">
-        <v>1140030</v>
+        <v>10016</v>
       </c>
       <c r="D93" t="n">
-        <v>1140050</v>
+        <v>1140051</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>enemy.voidranger-eliminator.minionlv2.variant.01</t>
+          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>110</v>
+        <v>1140012</v>
       </c>
       <c r="C94" t="n">
-        <v>10016</v>
+        <v>1140032</v>
       </c>
       <c r="D94" t="n">
-        <v>1140051</v>
+        <v>1140052</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
+          <t>enemy.voidranger-trampler-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1140012</v>
+        <v>111</v>
       </c>
       <c r="C95" t="n">
-        <v>1140032</v>
+        <v>10017</v>
       </c>
       <c r="D95" t="n">
-        <v>1140052</v>
+        <v>1150041</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>enemy.voidranger-trampler-bug.elite.variant.01</t>
+          <t>enemy.voidranger-trampler.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1150022</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1150042</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>enemy.windspawn.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1150023</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1150043</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>enemy.wraith-warden.minionlv2.variant.01</t>
         </is>
       </c>
     </row>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,273 +601,1441 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>10006</v>
+        <v>10007</v>
       </c>
       <c r="D8" t="n">
-        <v>13006</v>
+        <v>13007</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
+          <t>enemy.eclipse-wolftrooper.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>10007</v>
+        <v>10011</v>
       </c>
       <c r="D9" t="n">
-        <v>13007</v>
+        <v>13011</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>enemy.eclipse-wolftrooper.minionlv2.variant.01</t>
+          <t>enemy.harmonious-choir-the-great-septimus.bigboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C10" t="n">
-        <v>10008</v>
+        <v>10015</v>
       </c>
       <c r="D10" t="n">
-        <v>13008</v>
+        <v>13015</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
+          <t>enemy.sableclaw-wolftrooper.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C11" t="n">
-        <v>10009</v>
+        <v>10004</v>
       </c>
       <c r="D11" t="n">
-        <v>13009</v>
+        <v>13004</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>enemy.flamespawn.minion.variant.01</t>
+          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>104</v>
+        <v>980001</v>
       </c>
       <c r="C12" t="n">
-        <v>10010</v>
+        <v>980002</v>
       </c>
       <c r="D12" t="n">
-        <v>13010</v>
+        <v>980010</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>enemy.frostspawn.minion.variant.01</t>
+          <t>enemy.abundant-ebon-deer-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>105</v>
+        <v>990001</v>
       </c>
       <c r="C13" t="n">
-        <v>10011</v>
+        <v>990002</v>
       </c>
       <c r="D13" t="n">
-        <v>13011</v>
+        <v>990010</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>enemy.harmonious-choir-the-great-septimus.bigboss.variant.01</t>
+          <t>enemy.automaton-direwolf-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>106</v>
+        <v>1000001</v>
       </c>
       <c r="C14" t="n">
-        <v>10012</v>
+        <v>1000002</v>
       </c>
       <c r="D14" t="n">
-        <v>13012</v>
+        <v>1000010</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
+          <t>enemy.automaton-grizzly-complete.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>107</v>
+        <v>1010001</v>
       </c>
       <c r="C15" t="n">
-        <v>10013</v>
+        <v>1010002</v>
       </c>
       <c r="D15" t="n">
-        <v>13013</v>
+        <v>1010010</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
+          <t>enemy.blaze-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>108</v>
+        <v>1020001</v>
       </c>
       <c r="C16" t="n">
-        <v>10014</v>
+        <v>1020002</v>
       </c>
       <c r="D16" t="n">
-        <v>13014</v>
+        <v>1020010</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
+          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>109</v>
+        <v>1030001</v>
       </c>
       <c r="C17" t="n">
-        <v>10015</v>
+        <v>1030002</v>
       </c>
       <c r="D17" t="n">
-        <v>13015</v>
+        <v>1030010</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>enemy.sableclaw-wolftrooper.minionlv2.variant.01</t>
+          <t>enemy.cocolia-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>110</v>
+        <v>1040001</v>
       </c>
       <c r="C18" t="n">
-        <v>10016</v>
+        <v>1040002</v>
       </c>
       <c r="D18" t="n">
-        <v>13016</v>
+        <v>1040010</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
+          <t>enemy.gepard-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>111</v>
+        <v>1050001</v>
       </c>
       <c r="C19" t="n">
-        <v>10017</v>
+        <v>1050002</v>
       </c>
       <c r="D19" t="n">
-        <v>13017</v>
+        <v>1050010</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>enemy.voidranger-trampler.elite.variant.01</t>
+          <t>enemy.ice-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>95</v>
+        <v>1060001</v>
       </c>
       <c r="C20" t="n">
-        <v>10001</v>
+        <v>1060002</v>
       </c>
       <c r="D20" t="n">
-        <v>13001</v>
+        <v>1060010</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
+          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>96</v>
+        <v>1070001</v>
       </c>
       <c r="C21" t="n">
-        <v>10002</v>
+        <v>1070002</v>
       </c>
       <c r="D21" t="n">
-        <v>13002</v>
+        <v>1070010</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
+          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>97</v>
+        <v>1080001</v>
       </c>
       <c r="C22" t="n">
-        <v>10003</v>
+        <v>1080002</v>
       </c>
       <c r="D22" t="n">
-        <v>13003</v>
+        <v>1080010</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>enemy.automaton-spider.minionlv2.variant.01</t>
+          <t>enemy.svarog-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C23" t="n">
-        <v>10004</v>
+        <v>10001</v>
       </c>
       <c r="D23" t="n">
-        <v>13004</v>
+        <v>1090041</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
+          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1090022</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1090042</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1090023</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1090043</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1090024</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1090044</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1090025</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1090045</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>enemy.antibaryon.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1090026</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1090046</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>96</v>
+      </c>
+      <c r="C29" t="n">
+        <v>10002</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1090028</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1090048</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1090029</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1090049</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1090030</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1090050</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>enemy.automaton-direwolf.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1090031</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>enemy.automaton-grizzly.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1090032</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1090052</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>enemy.automaton-hound.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>97</v>
+      </c>
+      <c r="C35" t="n">
+        <v>10003</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1100041</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>enemy.automaton-spider.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1100022</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1100042</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>enemy.baryon.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1100023</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1100043</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>enemy.cloud-knights-patroller.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1100024</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1100044</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>enemy.decaying-shadow.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
         <v>99</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C39" t="n">
         <v>10005</v>
       </c>
-      <c r="D24" t="n">
-        <v>13005</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="D39" t="n">
+        <v>1100045</v>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1100026</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1100046</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>enemy.disciples-of-sanctus-medicus-internal-alchemist.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1100027</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1100047</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>100</v>
+      </c>
+      <c r="C42" t="n">
+        <v>10006</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1100048</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1100029</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1100030</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1100031</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1100051</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-birdskull.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1100032</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1100052</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-bubble-hound.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1110021</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1110041</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-mr-domescreen.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1110022</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1110042</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-spring-loader.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1110023</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1110043</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-sweet-gorilla-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1110024</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1110044</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-sweet-gorilla.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1110025</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1110045</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>enemy.dreamjolt-troupes-winder-goon.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1110026</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1110046</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>enemy.entranced-ingenium-golden-cloud-toad.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>102</v>
+      </c>
+      <c r="C53" t="n">
+        <v>10008</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1110047</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1110028</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1110048</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>enemy.entranced-ingenium-obedient-dracolion.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1110029</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1110049</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>enemy.everwinter-shadewalker.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>103</v>
+      </c>
+      <c r="C56" t="n">
+        <v>10009</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1110050</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>enemy.flamespawn.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1110031</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>enemy.frigid-prowler.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>104</v>
+      </c>
+      <c r="C58" t="n">
+        <v>10010</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1110052</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>enemy.frostspawn.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1120021</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1120041</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>enemy.grunt-field-personnel.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1120022</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1120042</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>enemy.grunt-security-personnel.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1120023</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>enemy.guardian-shadow.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1120024</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1120044</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>enemy.imaginary-weaver.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>106</v>
+      </c>
+      <c r="C63" t="n">
+        <v>10012</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1120045</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1120026</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1120046</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>enemy.juvenile-sting.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1120027</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1120047</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>enemy.lesser-sting.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>107</v>
+      </c>
+      <c r="C66" t="n">
+        <v>10013</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1120048</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>108</v>
+      </c>
+      <c r="C67" t="n">
+        <v>10014</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1120049</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1120030</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1120050</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>enemy.mask-of-no-thought.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1120031</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1120051</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>enemy.memory-zone-meme-allseer.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1120032</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1120052</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>enemy.memory-zone-meme-heartbreaker.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1130021</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1130041</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>enemy.memory-zone-meme-shell-of-faded-rage.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1130022</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1130042</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>enemy.memory-zone-meme-something-in-the-mirror.minionlv2.variant.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1130023</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1130043</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>enemy.searing-prowler.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1130024</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1130044</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>enemy.senior-staff-team-leader-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1130025</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1130045</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>enemy.senior-staff-team-leader.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1130026</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1130046</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>enemy.silvermane-cannoneer.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1130027</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1130047</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>enemy.silvermane-gunner.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1130028</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1130048</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>enemy.silvermane-lieutenant-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1130029</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1130049</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>enemy.silvermane-soldier.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1130030</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1130050</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>enemy.stormbringer-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1130031</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1130051</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>enemy.stormbringer.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1130032</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1130052</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>enemy.the-ascended.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1140021</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1140041</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>enemy.thunderspawn.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1140022</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1140042</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>enemy.trotter-of-abundance.minionlv2.02.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1140023</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1140043</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>enemy.trotter-of-abundance.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1140024</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1140044</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>enemy.trotter-of-destruction.minionlv2.02.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1140025</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1140045</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>enemy.trotter-of-destruction.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1140026</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1140046</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>enemy.trotter-of-preservation.minionlv2.03.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1140027</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1140047</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>enemy.trotter-of-preservation.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1140028</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1140048</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>enemy.vagrant.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1140029</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1140049</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>enemy.voidranger-distorter.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1140030</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1140050</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>enemy.voidranger-eliminator.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>110</v>
+      </c>
+      <c r="C93" t="n">
+        <v>10016</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1140051</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1140032</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>enemy.voidranger-trampler-bug.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>111</v>
+      </c>
+      <c r="C95" t="n">
+        <v>10017</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1150041</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>enemy.voidranger-trampler.elite.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1150022</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1150042</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>enemy.windspawn.minion.variant.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1150023</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1150043</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>enemy.wraith-warden.minionlv2.variant.01</t>
         </is>
       </c>
     </row>

--- a/config/data/EnemyVariant.xlsx
+++ b/config/data/EnemyVariant.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyVariant" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyVariant" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,16 +24,68 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,12 +93,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,200 +499,219 @@
   </sheetPr>
   <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="23.7109375" customWidth="1" style="5" min="2" max="2"/>
+    <col width="21.7109375" customWidth="1" style="5" min="3" max="3"/>
+    <col width="15.7109375" customWidth="1" style="5" min="4" max="4"/>
+    <col width="25.7109375" customWidth="1" style="5" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>@table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>EnemyVariant</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>@mode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>@key</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>@scope</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>@schema</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>04a17606a419bd3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>570cbbf84f38197e</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>#name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>template_id</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>ai_graph_id</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>mechanically_distinct_key</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>#field</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>template_id</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>ai_graph_id</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>mechanically_distinct_key</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>#type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>ref&lt;ContentIdentity.id&gt;</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>ref&lt;EnemyTemplate.id&gt;</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>ref&lt;AiGraph.id&gt;</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>#scope</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>all</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>#input</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>length=1..160</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" t="n">
-        <v>101</v>
-      </c>
-      <c r="C8" t="n">
-        <v>10007</v>
-      </c>
-      <c r="D8" t="n">
-        <v>13007</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10007</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>13007</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -616,14 +720,20 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>105</v>
-      </c>
-      <c r="C9" t="n">
-        <v>10011</v>
-      </c>
-      <c r="D9" t="n">
-        <v>13011</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10011</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>13011</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -632,14 +742,20 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>109</v>
-      </c>
-      <c r="C10" t="n">
-        <v>10015</v>
-      </c>
-      <c r="D10" t="n">
-        <v>13015</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10015</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>13015</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -648,14 +764,20 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>98</v>
-      </c>
-      <c r="C11" t="n">
-        <v>10004</v>
-      </c>
-      <c r="D11" t="n">
-        <v>13004</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10004</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>13004</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -664,14 +786,20 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>980001</v>
-      </c>
-      <c r="C12" t="n">
-        <v>980002</v>
-      </c>
-      <c r="D12" t="n">
-        <v>980010</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>980001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>980002</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>980010</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -680,14 +808,20 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>990001</v>
-      </c>
-      <c r="C13" t="n">
-        <v>990002</v>
-      </c>
-      <c r="D13" t="n">
-        <v>990010</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>990001</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>990002</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>990010</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -696,14 +830,20 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1000002</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1000010</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1000002</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1000010</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -712,14 +852,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>1010001</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1010002</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1010010</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1010001</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1010002</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1010010</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -728,1314 +874,1722 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>1020001</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1020002</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1020010</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1040001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1040002</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1040010</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
+          <t>enemy.gepard-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>1030001</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1030002</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1030010</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1050001</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1050002</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1050010</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>enemy.cocolia-complete.littleboss.variant.01</t>
+          <t>enemy.ice-out-of-space.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
-        <v>1040001</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1040002</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1040010</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1060001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1060002</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1060010</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>enemy.gepard-complete.littleboss.variant.01</t>
+          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
-        <v>1050001</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1050002</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1050010</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1070001</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1070002</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1070010</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>enemy.ice-out-of-space.elite.variant.01</t>
+          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
-        <v>1060001</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1060002</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1060010</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1080001</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1080002</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1080010</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-something-unto-death-complete.littleboss.variant.01</t>
+          <t>enemy.svarog-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
-        <v>1070001</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1070002</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1070010</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1090041</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>enemy.stellaron-hunter-kafka-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
-        <v>1080001</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1080002</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1080010</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1090002</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1090022</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1090042</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>enemy.svarog-complete.littleboss.variant.01</t>
+          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>95</v>
-      </c>
-      <c r="C23" t="n">
-        <v>10001</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1090041</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1090003</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1090023</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1090043</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
+          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
-        <v>1090002</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1090022</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1090042</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1090004</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1090024</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1090044</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-malefic-ape-bug.elite.variant.01</t>
+          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
-        <v>1090003</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1090023</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1090043</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1090005</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1090025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1090045</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-malefic-ape.elite.variant.01</t>
+          <t>enemy.antibaryon.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
-        <v>1090004</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1090024</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1090044</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1090006</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1090026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1090046</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>enemy.abundance-sprite-wooden-lupus.minionlv2.variant.01</t>
+          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
-        <v>1090005</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1090025</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1090045</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>10002</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1090047</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>enemy.antibaryon.minion.variant.01</t>
+          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
-        <v>1090006</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1090026</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1090046</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1090008</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1090028</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1090048</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper-bug.elite.variant.01</t>
+          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
-        <v>96</v>
-      </c>
-      <c r="C29" t="n">
-        <v>10002</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1090047</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1090009</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1090029</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1090049</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-gatekeeper.elite.variant.01</t>
+          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
-        <v>1090008</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1090028</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1090048</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1090010</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1090030</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1090050</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>enemy.aurumaton-spectral-envoy.elite.variant.01</t>
+          <t>enemy.automaton-direwolf.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
-        <v>1090009</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1090029</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1090049</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1090011</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1090031</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1090051</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>enemy.automaton-beetle.minionlv2.variant.01</t>
+          <t>enemy.automaton-grizzly.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="n">
-        <v>1090010</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1090030</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1090050</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1090012</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1090032</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1090052</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>enemy.automaton-direwolf.elite.variant.01</t>
+          <t>enemy.automaton-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
-        <v>1090011</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1090031</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1090051</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10003</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1100041</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>enemy.automaton-grizzly.elite.variant.01</t>
+          <t>enemy.automaton-spider.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
-        <v>1090012</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1090032</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1090052</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1100002</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1100022</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1100042</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>enemy.automaton-hound.minionlv2.variant.01</t>
+          <t>enemy.baryon.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
-        <v>97</v>
-      </c>
-      <c r="C35" t="n">
-        <v>10003</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1100041</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1100003</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1100023</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1100043</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>enemy.automaton-spider.minionlv2.variant.01</t>
+          <t>enemy.cloud-knights-patroller.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
-        <v>1100002</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1100022</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1100042</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1100004</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1100024</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1100044</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>enemy.baryon.minion.variant.01</t>
+          <t>enemy.decaying-shadow.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="n">
-        <v>1100003</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1100023</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1100043</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>10005</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1100045</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>enemy.cloud-knights-patroller.minionlv2.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="n">
-        <v>1100004</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1100024</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1100044</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1100006</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1100026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1100046</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>enemy.decaying-shadow.elite.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-internal-alchemist.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="n">
-        <v>99</v>
-      </c>
-      <c r="C39" t="n">
-        <v>10005</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1100045</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1100007</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1100027</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1100047</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="n">
-        <v>1100006</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1100026</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1100046</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>10006</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1100048</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-internal-alchemist.minionlv2.variant.01</t>
+          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="n">
-        <v>1100007</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1100027</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1100047</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1100009</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1100029</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1100049</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-shape-shifter-bug.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="n">
-        <v>100</v>
-      </c>
-      <c r="C42" t="n">
-        <v>10006</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1100048</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1100010</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1100030</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1100050</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-beyond-overcooked.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="n">
-        <v>1100009</v>
-      </c>
-      <c r="C43" t="n">
-        <v>1100029</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1100049</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1100011</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1100031</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1100051</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-beyond-overcooked-bug.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-birdskull.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="n">
-        <v>1100010</v>
-      </c>
-      <c r="C44" t="n">
-        <v>1100030</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1100050</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1100012</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1100032</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1100052</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-beyond-overcooked.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-bubble-hound.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="n">
-        <v>1100011</v>
-      </c>
-      <c r="C45" t="n">
-        <v>1100031</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1100051</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1110001</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1110021</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1110041</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-birdskull.minion.variant.01</t>
+          <t>enemy.dreamjolt-troupes-mr-domescreen.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="n">
-        <v>1100012</v>
-      </c>
-      <c r="C46" t="n">
-        <v>1100032</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1100052</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1110002</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1110022</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1110042</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-bubble-hound.minionlv2.variant.01</t>
+          <t>enemy.dreamjolt-troupes-spring-loader.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="n">
-        <v>1110001</v>
-      </c>
-      <c r="C47" t="n">
-        <v>1110021</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1110041</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1110003</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1110023</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1110043</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-mr-domescreen.minionlv2.variant.01</t>
+          <t>enemy.dreamjolt-troupes-sweet-gorilla-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="n">
-        <v>1110002</v>
-      </c>
-      <c r="C48" t="n">
-        <v>1110022</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1110042</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1110004</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1110024</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1110044</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-spring-loader.minion.variant.01</t>
+          <t>enemy.dreamjolt-troupes-sweet-gorilla.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="n">
-        <v>1110003</v>
-      </c>
-      <c r="C49" t="n">
-        <v>1110023</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1110043</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1110005</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1110025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1110045</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-sweet-gorilla-bug.elite.variant.01</t>
+          <t>enemy.dreamjolt-troupes-winder-goon.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="n">
-        <v>1110004</v>
-      </c>
-      <c r="C50" t="n">
-        <v>1110024</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1110044</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1110006</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1110026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1110046</t>
+        </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-sweet-gorilla.elite.variant.01</t>
+          <t>enemy.entranced-ingenium-golden-cloud-toad.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="n">
-        <v>1110005</v>
-      </c>
-      <c r="C51" t="n">
-        <v>1110025</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1110045</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>10008</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1110047</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>enemy.dreamjolt-troupes-winder-goon.minionlv2.variant.01</t>
+          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="n">
-        <v>1110006</v>
-      </c>
-      <c r="C52" t="n">
-        <v>1110026</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1110046</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1110008</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1110028</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1110048</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-golden-cloud-toad.minion.variant.01</t>
+          <t>enemy.entranced-ingenium-obedient-dracolion.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="n">
-        <v>102</v>
-      </c>
-      <c r="C53" t="n">
-        <v>10008</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1110047</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1110009</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1110029</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1110049</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
+          <t>enemy.everwinter-shadewalker.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="n">
-        <v>1110008</v>
-      </c>
-      <c r="C54" t="n">
-        <v>1110028</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1110048</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>10009</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1110050</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>enemy.entranced-ingenium-obedient-dracolion.minion.variant.01</t>
+          <t>enemy.flamespawn.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="n">
-        <v>1110009</v>
-      </c>
-      <c r="C55" t="n">
-        <v>1110029</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1110049</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1110011</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1110031</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1110051</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>enemy.everwinter-shadewalker.minionlv2.variant.01</t>
+          <t>enemy.frigid-prowler.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="n">
-        <v>103</v>
-      </c>
-      <c r="C56" t="n">
-        <v>10009</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1110050</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>10010</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1110052</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>enemy.flamespawn.minion.variant.01</t>
+          <t>enemy.frostspawn.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="n">
-        <v>1110011</v>
-      </c>
-      <c r="C57" t="n">
-        <v>1110031</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1110051</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1120001</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1120021</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1120041</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>enemy.frigid-prowler.elite.variant.01</t>
+          <t>enemy.grunt-field-personnel.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="n">
-        <v>104</v>
-      </c>
-      <c r="C58" t="n">
-        <v>10010</v>
-      </c>
-      <c r="D58" t="n">
-        <v>1110052</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1120002</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1120022</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1120042</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>enemy.frostspawn.minion.variant.01</t>
+          <t>enemy.grunt-security-personnel.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="n">
-        <v>1120001</v>
-      </c>
-      <c r="C59" t="n">
-        <v>1120021</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1120041</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1120003</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1120023</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1120043</t>
+        </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>enemy.grunt-field-personnel.minionlv2.variant.01</t>
+          <t>enemy.guardian-shadow.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="n">
-        <v>1120002</v>
-      </c>
-      <c r="C60" t="n">
-        <v>1120022</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1120042</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1120004</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1120024</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1120044</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>enemy.grunt-security-personnel.minionlv2.variant.01</t>
+          <t>enemy.imaginary-weaver.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="n">
-        <v>1120003</v>
-      </c>
-      <c r="C61" t="n">
-        <v>1120023</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1120043</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>10012</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1120045</t>
+        </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>enemy.guardian-shadow.elite.variant.01</t>
+          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="n">
-        <v>1120004</v>
-      </c>
-      <c r="C62" t="n">
-        <v>1120024</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1120044</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1120006</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1120026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1120046</t>
+        </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>enemy.imaginary-weaver.minionlv2.variant.01</t>
+          <t>enemy.juvenile-sting.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="n">
-        <v>106</v>
-      </c>
-      <c r="C63" t="n">
-        <v>10012</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1120045</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1120007</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1120027</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1120047</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>enemy.incineration-shadewalker.minionlv2.variant.01</t>
+          <t>enemy.lesser-sting.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="n">
-        <v>1120006</v>
-      </c>
-      <c r="C64" t="n">
-        <v>1120026</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1120046</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>10013</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1120048</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>enemy.juvenile-sting.minionlv2.variant.01</t>
+          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="n">
-        <v>1120007</v>
-      </c>
-      <c r="C65" t="n">
-        <v>1120027</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1120047</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>10014</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1120049</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>enemy.lesser-sting.minionlv2.variant.01</t>
+          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="n">
-        <v>107</v>
-      </c>
-      <c r="C66" t="n">
-        <v>10013</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1120048</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1120010</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1120030</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1120050</t>
+        </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-soldier.minionlv2.variant.01</t>
+          <t>enemy.mask-of-no-thought.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="n">
-        <v>108</v>
-      </c>
-      <c r="C67" t="n">
-        <v>10014</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1120049</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1120011</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1120031</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1120051</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>enemy.mara-struck-warden.minionlv2.variant.01</t>
+          <t>enemy.memory-zone-meme-allseer.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="n">
-        <v>1120010</v>
-      </c>
-      <c r="C68" t="n">
-        <v>1120030</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1120050</v>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1120012</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1120032</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1120052</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>enemy.mask-of-no-thought.minion.variant.01</t>
+          <t>enemy.memory-zone-meme-heartbreaker.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="n">
-        <v>1120011</v>
-      </c>
-      <c r="C69" t="n">
-        <v>1120031</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1120051</v>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1130001</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1130021</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1130041</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-allseer.minion.variant.01</t>
+          <t>enemy.memory-zone-meme-shell-of-faded-rage.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="n">
-        <v>1120012</v>
-      </c>
-      <c r="C70" t="n">
-        <v>1120032</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1120052</v>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1130002</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1130022</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1130042</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-heartbreaker.minionlv2.variant.01</t>
+          <t>enemy.memory-zone-meme-something-in-the-mirror.minionlv2.variant.02</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="n">
-        <v>1130001</v>
-      </c>
-      <c r="C71" t="n">
-        <v>1130021</v>
-      </c>
-      <c r="D71" t="n">
-        <v>1130041</v>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1130003</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1130023</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1130043</t>
+        </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-shell-of-faded-rage.elite.variant.01</t>
+          <t>enemy.searing-prowler.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="n">
-        <v>1130002</v>
-      </c>
-      <c r="C72" t="n">
-        <v>1130022</v>
-      </c>
-      <c r="D72" t="n">
-        <v>1130042</v>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1130004</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1130024</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1130044</t>
+        </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>enemy.memory-zone-meme-something-in-the-mirror.minionlv2.variant.02</t>
+          <t>enemy.senior-staff-team-leader-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="n">
-        <v>1130003</v>
-      </c>
-      <c r="C73" t="n">
-        <v>1130023</v>
-      </c>
-      <c r="D73" t="n">
-        <v>1130043</v>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1130005</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1130025</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1130045</t>
+        </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>enemy.searing-prowler.elite.variant.01</t>
+          <t>enemy.senior-staff-team-leader.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="n">
-        <v>1130004</v>
-      </c>
-      <c r="C74" t="n">
-        <v>1130024</v>
-      </c>
-      <c r="D74" t="n">
-        <v>1130044</v>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1130006</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1130026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1130046</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>enemy.senior-staff-team-leader-bug.elite.variant.01</t>
+          <t>enemy.silvermane-cannoneer.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="n">
-        <v>1130005</v>
-      </c>
-      <c r="C75" t="n">
-        <v>1130025</v>
-      </c>
-      <c r="D75" t="n">
-        <v>1130045</v>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1130007</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1130027</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1130047</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>enemy.senior-staff-team-leader.elite.variant.01</t>
+          <t>enemy.silvermane-gunner.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="n">
-        <v>1130006</v>
-      </c>
-      <c r="C76" t="n">
-        <v>1130026</v>
-      </c>
-      <c r="D76" t="n">
-        <v>1130046</v>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1130008</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1130028</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1130048</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>enemy.silvermane-cannoneer.minionlv2.variant.01</t>
+          <t>enemy.silvermane-lieutenant-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="n">
-        <v>1130007</v>
-      </c>
-      <c r="C77" t="n">
-        <v>1130027</v>
-      </c>
-      <c r="D77" t="n">
-        <v>1130047</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1130009</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1130029</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1130049</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>enemy.silvermane-gunner.minionlv2.variant.01</t>
+          <t>enemy.silvermane-soldier.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" t="n">
-        <v>1130008</v>
-      </c>
-      <c r="C78" t="n">
-        <v>1130028</v>
-      </c>
-      <c r="D78" t="n">
-        <v>1130048</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1130010</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1130030</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1130050</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>enemy.silvermane-lieutenant-bug.elite.variant.01</t>
+          <t>enemy.stormbringer-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="n">
-        <v>1130009</v>
-      </c>
-      <c r="C79" t="n">
-        <v>1130029</v>
-      </c>
-      <c r="D79" t="n">
-        <v>1130049</v>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1130011</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1130031</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1130051</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>enemy.silvermane-soldier.minionlv2.variant.01</t>
+          <t>enemy.stormbringer.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="n">
-        <v>1130010</v>
-      </c>
-      <c r="C80" t="n">
-        <v>1130030</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1130050</v>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1130012</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1130032</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1130052</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>enemy.stormbringer-bug.elite.variant.01</t>
+          <t>enemy.the-ascended.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" t="n">
-        <v>1130011</v>
-      </c>
-      <c r="C81" t="n">
-        <v>1130031</v>
-      </c>
-      <c r="D81" t="n">
-        <v>1130051</v>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>10017</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1150041</t>
+        </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>enemy.stormbringer.elite.variant.01</t>
+          <t>enemy.voidranger-trampler.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="n">
-        <v>1130012</v>
-      </c>
-      <c r="C82" t="n">
-        <v>1130032</v>
-      </c>
-      <c r="D82" t="n">
-        <v>1130052</v>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1150002</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1150022</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1150042</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>enemy.the-ascended.elite.variant.01</t>
+          <t>enemy.windspawn.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" t="n">
-        <v>1140001</v>
-      </c>
-      <c r="C83" t="n">
-        <v>1140021</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1140041</v>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1150003</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1150023</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1150043</t>
+        </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>enemy.thunderspawn.minion.variant.01</t>
+          <t>enemy.wraith-warden.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1140002</v>
+        <v>1020001</v>
       </c>
       <c r="C84" t="n">
-        <v>1140022</v>
+        <v>1020002</v>
       </c>
       <c r="D84" t="n">
-        <v>1140042</v>
+        <v>1020010</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>enemy.trotter-of-abundance.minionlv2.02.variant.01</t>
+          <t>enemy.cloud-knight-lieutenant-yanqing-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1140003</v>
+        <v>1140001</v>
       </c>
       <c r="C85" t="n">
-        <v>1140023</v>
+        <v>1140021</v>
       </c>
       <c r="D85" t="n">
-        <v>1140043</v>
+        <v>1140041</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>enemy.trotter-of-abundance.minionlv2.variant.01</t>
+          <t>enemy.thunderspawn.minion.variant.01</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1140004</v>
+        <v>1140002</v>
       </c>
       <c r="C86" t="n">
-        <v>1140024</v>
+        <v>1140022</v>
       </c>
       <c r="D86" t="n">
-        <v>1140044</v>
+        <v>1140042</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>enemy.trotter-of-destruction.minionlv2.02.variant.01</t>
+          <t>enemy.trotter-of-abundance.minionlv2.02.variant.01</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1140005</v>
+        <v>1140003</v>
       </c>
       <c r="C87" t="n">
-        <v>1140025</v>
+        <v>1140023</v>
       </c>
       <c r="D87" t="n">
-        <v>1140045</v>
+        <v>1140043</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>enemy.trotter-of-destruction.minionlv2.variant.01</t>
+          <t>enemy.trotter-of-abundance.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1140006</v>
+        <v>1140004</v>
       </c>
       <c r="C88" t="n">
-        <v>1140026</v>
+        <v>1140024</v>
       </c>
       <c r="D88" t="n">
-        <v>1140046</v>
+        <v>1140044</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>enemy.trotter-of-preservation.minionlv2.03.variant.01</t>
+          <t>enemy.trotter-of-destruction.minionlv2.02.variant.01</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1140007</v>
+        <v>1140005</v>
       </c>
       <c r="C89" t="n">
-        <v>1140027</v>
+        <v>1140025</v>
       </c>
       <c r="D89" t="n">
-        <v>1140047</v>
+        <v>1140045</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>enemy.trotter-of-preservation.minionlv2.variant.01</t>
+          <t>enemy.trotter-of-destruction.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1140008</v>
+        <v>1140006</v>
       </c>
       <c r="C90" t="n">
-        <v>1140028</v>
+        <v>1140026</v>
       </c>
       <c r="D90" t="n">
-        <v>1140048</v>
+        <v>1140046</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>enemy.vagrant.minionlv2.variant.01</t>
+          <t>enemy.trotter-of-preservation.minionlv2.03.variant.01</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1140009</v>
+        <v>1140007</v>
       </c>
       <c r="C91" t="n">
-        <v>1140029</v>
+        <v>1140027</v>
       </c>
       <c r="D91" t="n">
-        <v>1140049</v>
+        <v>1140047</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>enemy.voidranger-distorter.minionlv2.variant.01</t>
+          <t>enemy.trotter-of-preservation.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1140010</v>
+        <v>1140008</v>
       </c>
       <c r="C92" t="n">
-        <v>1140030</v>
+        <v>1140028</v>
       </c>
       <c r="D92" t="n">
-        <v>1140050</v>
+        <v>1140048</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>enemy.voidranger-eliminator.minionlv2.variant.01</t>
+          <t>enemy.vagrant.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>110</v>
+        <v>1140009</v>
       </c>
       <c r="C93" t="n">
-        <v>10016</v>
+        <v>1140029</v>
       </c>
       <c r="D93" t="n">
-        <v>1140051</v>
+        <v>1140049</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
+          <t>enemy.voidranger-distorter.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1140012</v>
+        <v>1140010</v>
       </c>
       <c r="C94" t="n">
-        <v>1140032</v>
+        <v>1140030</v>
       </c>
       <c r="D94" t="n">
-        <v>1140052</v>
+        <v>1140050</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>enemy.voidranger-trampler-bug.elite.variant.01</t>
+          <t>enemy.voidranger-eliminator.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C95" t="n">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="D95" t="n">
-        <v>1150041</v>
+        <v>1140051</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>enemy.voidranger-trampler.elite.variant.01</t>
+          <t>enemy.voidranger-reaver.minionlv2.variant.01</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1150002</v>
+        <v>1140012</v>
       </c>
       <c r="C96" t="n">
-        <v>1150022</v>
+        <v>1140032</v>
       </c>
       <c r="D96" t="n">
-        <v>1150042</v>
+        <v>1140052</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>enemy.windspawn.minion.variant.01</t>
+          <t>enemy.voidranger-trampler-bug.elite.variant.01</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1150003</v>
+        <v>1030001</v>
       </c>
       <c r="C97" t="n">
-        <v>1150023</v>
+        <v>1030002</v>
       </c>
       <c r="D97" t="n">
-        <v>1150043</v>
+        <v>1030010</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>enemy.wraith-warden.minionlv2.variant.01</t>
+          <t>enemy.cocolia-complete.littleboss.variant.01</t>
         </is>
       </c>
     </row>
